--- a/output/full_scan/batch_seq4_2026-09-24.xlsx
+++ b/output/full_scan/batch_seq4_2026-09-24.xlsx
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>73.61262508534342</v>
+        <v>73.61262511635334</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>20.01966482600456</v>
+        <v>20.01966497108525</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>2.256065661144051</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>53.07681502743094</v>
+        <v>53.07681500991646</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>67.03687081657515</v>
+        <v>67.03687083488224</v>
       </c>
       <c r="I3" s="2" t="n">
         <v>21.50678527587094</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>6.515014567954089</v>
+        <v>6.515014567438964</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66.12696407915226</v>
+        <v>66.1269640827113</v>
       </c>
       <c r="I4" s="2" t="n">
         <v>15.2146541959244</v>
@@ -676,7 +676,7 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>12.40359530907022</v>
+        <v>12.40359530876109</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>72.16689467444202</v>
+        <v>72.16689468558531</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>33.88548430721701</v>
+        <v>33.88548433928054</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>5.123988169742399</v>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>76.24830780484352</v>
+        <v>76.24830779956694</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>38.37873979025451</v>
+        <v>38.37873979978102</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>1.680779748390488</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>2.145270549474349</v>
+        <v>2.145270549690713</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>70.6277070828486</v>
+        <v>70.62770706635015</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>34.8147225077081</v>
+        <v>34.81472244938559</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>2.179618110693879</v>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>67.11364206611364</v>
+        <v>67.11364208435876</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>14.84574790645573</v>
+        <v>14.8457479161741</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>0.5958135246986367</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>9.768803597081058</v>
+        <v>9.768803596050692</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>64.685744950703</v>
+        <v>64.68574495859956</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>41.79902490392947</v>
+        <v>41.79902486126949</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>1.121416808824015</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.391344159823479</v>
+        <v>-0.3913441599161977</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>67.87454424562742</v>
+        <v>67.87454425978945</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15.54758686141266</v>
+        <v>15.5475867926993</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>2.442862612192605</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>10.20235695072043</v>
+        <v>10.20235694896888</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1002.464051269196</v>
+        <v>1002.464051269198</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>949</v>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>64.77022450168445</v>
+        <v>64.77022451671013</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>18.76797479139835</v>
+        <v>18.76797480187767</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>1.55740912058492</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>5.493597248776119</v>
+        <v>5.493597246406473</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>63.08833581536791</v>
+        <v>63.0883358184707</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>28.27049493580112</v>
+        <v>28.27049494704369</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>8.535996842204639</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.670598970675254</v>
+        <v>1.670598970757676</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>70.54873042294616</v>
+        <v>70.54873041751648</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>30.03639121069384</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.176275938373367</v>
+        <v>1.176275938393974</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>58.8291673306901</v>
+        <v>58.82916732694565</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>13.03647497385428</v>
+        <v>13.03647504196318</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>2.271120992378672</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.92513468430192</v>
+        <v>0.9251346844667624</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>79.5351160118218</v>
+        <v>79.53511601217886</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>40.64131457501446</v>
+        <v>40.6413145821616</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0.6882891185080461</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>5.219078931423375</v>
+        <v>5.219078931608834</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>73.32995743893753</v>
+        <v>73.32995744759307</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>32.55063786275031</v>
+        <v>32.55063785441009</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>1.362680603084347</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>21.84465127222644</v>
+        <v>21.84465127099004</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1333,7 +1333,7 @@
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>896.4669336631304</v>
+        <v>896.4669336631305</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>47.2</v>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>59.94634984783944</v>
+        <v>59.94634976631204</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>26.18344510677088</v>
+        <v>26.18344514914594</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1.817767666721637</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.2098499122920329</v>
+        <v>0.2098499129823237</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,7 +1400,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>62.60176724925214</v>
+        <v>62.60176723243313</v>
       </c>
       <c r="I18" s="2" t="n">
         <v>17.75894016691775</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.1722564124855513</v>
+        <v>0.1722564124937922</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>64.07434279971554</v>
+        <v>64.07434281064116</v>
       </c>
       <c r="I19" s="2" t="n">
         <v>17.01398457651544</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.531836508676994</v>
+        <v>1.531836508738802</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>68.84309064017957</v>
+        <v>68.84309065202456</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>18.39980670550706</v>
+        <v>18.39980672384296</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>3.85118759147017</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.43108627413324</v>
+        <v>1.43108627425687</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>841.8035123128225</v>
+        <v>841.8035123128224</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>452.5</v>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>63.57934129303893</v>
+        <v>63.57934130478261</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>32.01222401881807</v>
+        <v>32.01222402240474</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.6301988159388836</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>2.033912041853693</v>
+        <v>2.033912041420969</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>832.9882605574227</v>
+        <v>832.9882605574228</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>2340</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>60.7141555700877</v>
+        <v>60.7141556281677</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15.67230233397184</v>
+        <v>15.67230250217718</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>1.36882934122329</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>40.89732103243659</v>
+        <v>40.89732102316363</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>72.74114424716115</v>
+        <v>72.74114423215178</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>52.07465073569679</v>
+        <v>52.07465052285972</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0.4287690140134053</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1286372871870515</v>
+        <v>0.1286372873003842</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>58.21834518846181</v>
+        <v>58.21834527532604</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>23.62171605404053</v>
+        <v>23.62171601084333</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>0.6346432281774312</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.1678888707800068</v>
+        <v>-0.1678888716042523</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>60.29423249283976</v>
+        <v>60.29423249583816</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>23.43726711302785</v>
+        <v>23.43726713489442</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>1.637735272203349</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.7470985797489975</v>
+        <v>0.7470985799138559</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>69.90824632833153</v>
+        <v>69.90824633488506</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>36.71325114314984</v>
+        <v>36.71325113209628</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>1.358764037325768</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.62659013492085</v>
+        <v>1.626590135003279</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>60.14462396211606</v>
+        <v>60.14462427410668</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>27.959736787992</v>
+        <v>27.95973680805202</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>1.98281625398306</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1706728121437737</v>
+        <v>0.1706728121128643</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>66.10959286486063</v>
+        <v>66.10959272038522</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>38.82875736179732</v>
+        <v>38.82875742084621</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>2.037158419477089</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.7117909650086449</v>
+        <v>0.7117909652559133</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>60.61864262916969</v>
+        <v>60.61864264631136</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>31.14629546439102</v>
+        <v>31.14629544912737</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>0.5533000623860974</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.2382324377972005</v>
+        <v>0.2382324378325182</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>802.3324330217339</v>
+        <v>802.332433021734</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>45.4</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>61.53213090151424</v>
+        <v>61.53213114977339</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20.83621479173243</v>
+        <v>20.83621481246016</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>5.646051563605955</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.3307534260727829</v>
+        <v>0.330753426113993</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>69.5694161595782</v>
+        <v>69.56941614386787</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>25.69929455277445</v>
+        <v>25.699294499795</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>6.856557300808712</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>3.552139129449239</v>
+        <v>3.552139129387421</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>58.17733872051885</v>
+        <v>58.17733871894136</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>13.65803264462744</v>
+        <v>13.65803266019826</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.5374173130016149</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>6.800993716623992</v>
+        <v>6.800993716108877</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>57.55460137288748</v>
+        <v>57.55460135244225</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>17.38536040866286</v>
+        <v>17.38536039384805</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.6722253325089924</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.2885020177913926</v>
+        <v>0.2885020185125562</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>60.93048039379954</v>
+        <v>60.93048037364278</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>40.13647662963114</v>
+        <v>40.13647676727416</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>1.110610536017054</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.0158544119520076</v>
+        <v>-0.0158544118180687</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>70.38719537151775</v>
+        <v>70.38719538372902</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>32.37932056013893</v>
+        <v>32.37932062668082</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.9221864814963022</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.5275376158017906</v>
+        <v>0.5275376161108341</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>65.8644459302957</v>
+        <v>65.86444599566585</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>20.38689087317968</v>
+        <v>20.3868908494191</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.8755146918912791</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>70.06539486560671</v>
+        <v>70.06539485015244</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>68.29430497602792</v>
+        <v>68.29430498802573</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>32.09538602797313</v>
+        <v>32.0953860385156</v>
       </c>
       <c r="J37" s="2" t="n">
         <v>1.485670689521542</v>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>65.39226119096958</v>
+        <v>65.39226151095465</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>37.72796671130293</v>
+        <v>37.72796679477382</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>1.076955423323244</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.3986211970672042</v>
+        <v>0.3986211967066057</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>78.4263683045512</v>
+        <v>78.42636828448555</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>52.96359614606145</v>
+        <v>52.96359619150951</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>1.002387116603794</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>2.660901038744345</v>
+        <v>2.660901038888585</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>56.81809455315066</v>
+        <v>56.81809455483162</v>
       </c>
       <c r="I41" s="2" t="n">
         <v>27.65672652504281</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-1.826789401184847</v>
+        <v>-1.826789401493954</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>61.23027504516352</v>
+        <v>61.23027504948998</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>28.63791921134429</v>
+        <v>28.63791921821767</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>0.5338240457739151</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.3197287707607601</v>
+        <v>0.3197287707813652</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>690.8936040989773</v>
+        <v>690.8936040989779</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>27.95</v>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>64.55654781288047</v>
+        <v>64.55654772389913</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>28.88532365643179</v>
+        <v>28.88532375739664</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.3782811262697764</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.3518805457103777</v>
+        <v>0.3518805458649227</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>685.7898084125557</v>
+        <v>685.7898084125552</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>99.40000000000001</v>
@@ -2778,7 +2778,7 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>63.53625063736025</v>
+        <v>63.53907149092338</v>
       </c>
       <c r="I44" s="2" t="n">
         <v>60.75726995059456</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.0528528602522777</v>
+        <v>-0.0528508898366056</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>55.81606936129703</v>
+        <v>55.81606937072959</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>28.44517506933177</v>
+        <v>28.44517507478029</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.447132927958286</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.0176086339322399</v>
+        <v>-0.0176086339528437</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>59.52018682592849</v>
+        <v>59.52018689673147</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>25.83270811049405</v>
+        <v>25.83270813267633</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.2741866501919323</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0952987276921797</v>
+        <v>0.0952987276200505</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>666.6744531969589</v>
+        <v>666.6744531969588</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>17.9</v>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>58.41316720440241</v>
+        <v>58.41316722019191</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>27.84416522124261</v>
+        <v>27.84416519308537</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>1.199312633526556</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0337447134964814</v>
+        <v>0.0337447135479966</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>664.4914835043752</v>
+        <v>664.4914835043749</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>68.90000000000001</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>59.25655314684855</v>
+        <v>59.25655297495057</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>23.43008427651277</v>
+        <v>23.43008427082232</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>1.490835057844686</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>1.097124341649401</v>
+        <v>1.097124342226361</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>54.77681431617417</v>
+        <v>54.77681424932954</v>
       </c>
       <c r="I49" s="2" t="n">
         <v>16.29680399831524</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1108759288628238</v>
+        <v>0.1108759288422169</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>57.15711060348089</v>
+        <v>57.1571106103292</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>18.37643423535303</v>
+        <v>18.37643424318943</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.6429291810658572</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.498138158327411</v>
+        <v>1.498138158409806</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>78.74736865820071</v>
+        <v>78.74736856468884</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>23.58618803038691</v>
+        <v>23.58618803269447</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>0.9967911928548756</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.3029352124566632</v>
+        <v>0.302935212508177</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>88.01990018162252</v>
+        <v>88.01990014082509</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>36.33915928402379</v>
+        <v>36.33916033774211</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.5729402479523195</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.3456221320599001</v>
+        <v>0.3456221323424175</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>614.33622690659</v>
+        <v>614.3362269065904</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>71.90000000000001</v>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>52.49674936048616</v>
+        <v>52.49674931172622</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>26.24824116417208</v>
+        <v>26.2482413080174</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.5040643032148443</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0019101195498844</v>
+        <v>0.0019101196941255</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>54.16815559909578</v>
+        <v>54.16815559731925</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>23.69965990077268</v>
+        <v>23.69965988477684</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>0.632245345795861</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.35061367213126</v>
+        <v>-0.3506136720797435</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>66.67182172072089</v>
+        <v>66.67182180324697</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>32.30610922646978</v>
+        <v>32.3061092455017</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>1.151031432412038</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>53.15943309595194</v>
+        <v>53.15943304156036</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>8.472045090242084</v>
+        <v>8.472045232979839</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.5893034644567916</v>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>51.42432254216561</v>
+        <v>51.42432268844757</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>20.36529064877289</v>
+        <v>20.36529064877288</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.6799845768712917</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>2.057348262862016</v>
+        <v>2.057348262140819</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.32037471970057</v>
+        <v>52.32037472815189</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>9.863708741893314</v>
+        <v>9.863708718972989</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>1.580138880361237</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.232982647941069</v>
+        <v>0.2329826479616757</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>58.63490319291088</v>
+        <v>58.63489639156941</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>17.16734241702018</v>
+        <v>17.16734245442693</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.4074975354292283</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.0147186945742759</v>
+        <v>-0.0147186945330642</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>65.274310074395</v>
+        <v>65.27431008465803</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>36.61748459827734</v>
+        <v>36.61748462085246</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.8011777735130025</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.4788556893695317</v>
+        <v>0.4788556894004383</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>52.26935856715917</v>
+        <v>52.26935854226889</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>12.93103354784098</v>
+        <v>12.93103359380409</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>2.748753193860966</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.1438794863125965</v>
+        <v>-0.143879486009828</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>570.6576712331714</v>
+        <v>570.6576712331699</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>45.65</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>58.46449898503023</v>
+        <v>58.46449926741292</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>28.89990216012724</v>
+        <v>28.8999021483184</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.3050180038402357</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.091328146456814</v>
+        <v>0.09132814700285929</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>567.1984696788932</v>
+        <v>567.1984696788935</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>8.859999999999999</v>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>58.08193064215224</v>
+        <v>58.08193065112616</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>10.56160768608002</v>
+        <v>10.56160766964318</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>1.515627426154144</v>
@@ -3856,7 +3856,7 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.079919590243185</v>
+        <v>0.07991959022257999</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>59.02102471579865</v>
+        <v>59.0210247393914</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>15.22941465295206</v>
+        <v>15.229414617035</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>6.934148303290059</v>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>53.58832900851168</v>
+        <v>53.58832895225821</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>4.247525626852188</v>
+        <v>4.247525626940332</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.2090974515380325</v>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>52.82989181833386</v>
+        <v>52.82989169646092</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>22.41723146917148</v>
+        <v>22.41723156377933</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.7483535274785388</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0362359041246308</v>
+        <v>0.0362359041864478</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>554.9982039509496</v>
+        <v>554.9982039509497</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>123</v>
@@ -4050,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>51.07922722163067</v>
+        <v>51.07922728438911</v>
       </c>
       <c r="I68" s="2" t="n">
         <v>21.02267042648525</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.2722162736720764</v>
+        <v>0.2722162729714836</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>57.51659413186331</v>
+        <v>57.51659430202221</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>24.11480186914155</v>
+        <v>24.11480192249145</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>0.3334113220005095</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1256526763209628</v>
+        <v>-0.1256526768670149</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>549.8168824265989</v>
+        <v>549.8168824265987</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>31.6</v>
@@ -4156,7 +4156,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>57.73979760004484</v>
+        <v>57.73979758092193</v>
       </c>
       <c r="I70" s="2" t="n">
         <v>30.77486858663044</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.2132874694521618</v>
+        <v>0.2132874694727659</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>55.42056785983002</v>
+        <v>55.42056778558058</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>10.29954194779609</v>
+        <v>10.2995420425184</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.8667252815497062</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0859200087821004</v>
+        <v>0.0859200090911824</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>543.2419206084235</v>
+        <v>543.2419206084236</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>67.59999999999999</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>56.8498907958296</v>
+        <v>56.84989070168693</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>14.55933427199944</v>
+        <v>14.55933434214523</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.319663854112855</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.1278474871583275</v>
+        <v>0.1278474882710328</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>542.9692554257797</v>
+        <v>542.9692554257805</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>85</v>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>53.29219445757922</v>
+        <v>53.29219460372574</v>
       </c>
       <c r="I73" s="2" t="n">
         <v>13.30245626234925</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.541395103831644</v>
+        <v>0.5413951036461857</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>54.47113776675194</v>
+        <v>54.47113773359573</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>33.70032044314392</v>
+        <v>33.70032050486451</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.4577437211522194</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.3509748590816837</v>
+        <v>-0.350974858793202</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>55.18168980487067</v>
+        <v>55.1816900016985</v>
       </c>
       <c r="I75" s="2" t="n">
         <v>39.04840955724337</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0357385113511539</v>
+        <v>0.0357385113408506</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>66.80883599917742</v>
+        <v>66.80883600510377</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>31.99071135254935</v>
+        <v>31.99071139550221</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.6869807903016845</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.5815592727352055</v>
+        <v>0.5815592727764143</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>52.92873952821113</v>
+        <v>52.92873951360731</v>
       </c>
       <c r="I77" s="2" t="n">
         <v>26.4040844436471</v>
@@ -4566,7 +4566,7 @@
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>526.8458481738513</v>
+        <v>526.8458481738521</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>65.2</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>58.01557023659044</v>
+        <v>58.01557024748325</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>23.33848124517598</v>
+        <v>23.33848122353546</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.7940511965114355</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.3154570052171928</v>
+        <v>0.3154570054644012</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>522.41977849607</v>
+        <v>522.4197784960699</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>246</v>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>53.74011598133773</v>
+        <v>53.74011598074935</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>28.57092389551791</v>
+        <v>28.57092389436645</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>1.384760666645939</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>2.042176545345432</v>
+        <v>2.04217654516002</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>51.06084502833591</v>
+        <v>51.06084516031443</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>23.99054644517955</v>
+        <v>23.99054657031717</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.9131049899276608</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0523373651451741</v>
+        <v>-0.0523373650833563</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>51.66265534990396</v>
+        <v>51.66265542540339</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>18.49436291915298</v>
+        <v>18.49436293427526</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>1.529710217811603</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.4067247244526824</v>
+        <v>0.4067247239375462</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>54.90139697394701</v>
+        <v>54.90139696904161</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13.44033390804937</v>
+        <v>13.44033397399243</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>0.602275264324557</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.2072226134468848</v>
+        <v>0.207222613611731</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>513.6580529772891</v>
+        <v>513.6580529772893</v>
       </c>
       <c r="E83" s="2" t="n">
         <v>140</v>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>53.074689019494</v>
+        <v>53.0746889378585</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>20.04220740611282</v>
+        <v>20.04220741716327</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.941116231528476</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.7462597540234588</v>
+        <v>0.7462597544355734</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>511.6332271804631</v>
+        <v>511.6332271804632</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>129.5</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>57.9337159863231</v>
+        <v>57.93371603870958</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>17.72495738841602</v>
+        <v>17.72495741968742</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.9133972201883788</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.9721422281046082</v>
+        <v>0.9721422280839968</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>50.56233398599316</v>
+        <v>50.56233397767091</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>36.02496799026107</v>
+        <v>36.02496797227034</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.440245459880123</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-27.29501793601112</v>
+        <v>-27.29501793415659</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>507.8038562079749</v>
+        <v>507.8038562079751</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>27</v>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>55.95931519607432</v>
+        <v>55.95931510019174</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>29.28640158677745</v>
+        <v>29.28640157033431</v>
       </c>
       <c r="J86" s="2" t="n">
         <v>0.9299519607573308</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.060998225702176</v>
+        <v>0.0609982258464173</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5057,7 +5057,7 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>53.02031180132823</v>
+        <v>53.02031180690584</v>
       </c>
       <c r="I87" s="2" t="n">
         <v>24.25507067473984</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-4.062838317574126</v>
+        <v>-4.062838317738976</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>49.53369424508227</v>
+        <v>49.53369419575336</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>28.93407403222626</v>
+        <v>28.93407397514829</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>0.3586666804839356</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.7229850967734879</v>
+        <v>-0.7229850964540896</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>496.7616655577778</v>
+        <v>496.7616655577775</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>19.95</v>
@@ -5166,7 +5166,7 @@
         <v>63.30483404024913</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>18.46183632249016</v>
+        <v>18.46183634445809</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.8650570566434078</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.3527159758127504</v>
+        <v>0.3527159758436579</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>495.5080999184769</v>
+        <v>495.5080999184733</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>33.65</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>70.2742760137881</v>
+        <v>70.27427542657554</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>19.3555046757587</v>
+        <v>19.35550493693172</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>11.53683940844793</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.5341766680906885</v>
+        <v>0.5341766690282529</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>491.9868437599142</v>
+        <v>491.9868437599124</v>
       </c>
       <c r="E91" s="2" t="n">
         <v>37.9</v>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>55.55527846622105</v>
+        <v>55.55527847537834</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>16.24636739430447</v>
+        <v>16.24636739245034</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>1.278250770109548</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.477025908103533</v>
+        <v>0.4770259080932268</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>488.9697062450389</v>
+        <v>488.9697062450432</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>73.3</v>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>56.84050319304242</v>
+        <v>56.84050312077858</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>15.19200240621521</v>
+        <v>15.19200257943902</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>1.828765695686838</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.374728958282549</v>
+        <v>0.3747289588801181</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>52.56473340751752</v>
+        <v>52.56473340268518</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>20.00600338806856</v>
+        <v>20.00600346184982</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.6515106030108712</v>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>63.08695709611733</v>
+        <v>63.08695716592757</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>32.35591627012522</v>
+        <v>32.35591626480861</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.2336463290885963</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.1356532404741187</v>
+        <v>0.1356532404329077</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>470.555806867257</v>
+        <v>470.555806867258</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>31.6</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>55.08098029658992</v>
+        <v>55.08098021967093</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>30.66706200146162</v>
+        <v>30.6670619498494</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.5564768477308839</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.2153294276234476</v>
+        <v>0.2153294278604113</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>49.1254739980164</v>
+        <v>49.12547402685642</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>23.11894204439564</v>
+        <v>23.11894205179462</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.2880366545910341</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.2681981433945428</v>
+        <v>-0.2681981434357668</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>467.8018407383909</v>
+        <v>467.8018407383917</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>26.4</v>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>52.95709336537223</v>
+        <v>52.95709330092195</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>22.25731909003001</v>
+        <v>22.2573193300105</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>1.692165830509133</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.1696771717271863</v>
+        <v>0.1696771719435463</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>50.49259820047118</v>
+        <v>50.49259809245554</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>19.19761922815806</v>
+        <v>19.19761924429336</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.4732222217671081</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0744582442310775</v>
+        <v>-0.0744582442001606</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>44.83243787804745</v>
+        <v>44.83243791491911</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>25.80143096608883</v>
+        <v>25.80143097140458</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.3912502850070979</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-1.688366984365625</v>
+        <v>-1.68836698444805</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>37.8831900311849</v>
+        <v>37.88319000013469</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>30.3377681341905</v>
+        <v>30.33776824186238</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.328519018109024</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.4086961767520316</v>
+        <v>0.408696176855067</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>51.57365249596157</v>
+        <v>51.57365252661261</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>10.57339174723554</v>
+        <v>10.57339176201896</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.293230501522351</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>1.065842414577105</v>
+        <v>1.065842414783147</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>49.07070288320865</v>
+        <v>49.07070288827069</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>10.65147834014643</v>
+        <v>10.65147835867334</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.8867405720445148</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.1397540068514674</v>
+        <v>0.1397540068823819</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>439.4422189039534</v>
+        <v>439.4422189039535</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>2410</v>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>47.79096723468745</v>
+        <v>47.79096726663811</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>9.415019894952763</v>
+        <v>9.415020075529441</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.4473475238743477</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>9.304130740429912</v>
+        <v>9.304130727035876</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>49.74706534716448</v>
+        <v>49.74706536156252</v>
       </c>
       <c r="I104" s="2" t="n">
         <v>16.75058124338309</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.7255498582855411</v>
+        <v>-0.7255498580794582</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>436.9083382990862</v>
+        <v>436.9083382989696</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>61.5</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>51.81870189790902</v>
+        <v>51.81870189300484</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>5.731403935822069</v>
+        <v>5.731403913743681</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>1.745862463957025</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.09862317675529</v>
+        <v>0.0986231774249835</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>34.49763654980268</v>
+        <v>34.49763657104963</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>22.92777303240092</v>
+        <v>22.92777303240093</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>2.82263175611179</v>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>50.46431987083276</v>
+        <v>50.46431993187829</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15.03330888886029</v>
+        <v>15.0333089116541</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.4439708478300677</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-4.85231852571917</v>
+        <v>-4.852318554566985</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>57.80189290291966</v>
+        <v>57.80189296758745</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>30.46951965511496</v>
+        <v>30.46951963813871</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.1477160668102483</v>
@@ -6226,7 +6226,7 @@
         <v>52.3276091462652</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.17222510863482</v>
+        <v>13.17222514183875</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>1.662293121124835</v>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>49.54969239790112</v>
+        <v>49.54969243352448</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>18.15498653812729</v>
+        <v>18.1549865405423</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.7875355456852896</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1192283686467999</v>
+        <v>0.119228368636492</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>49.17057953872753</v>
+        <v>49.17057954787504</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>14.2341935203991</v>
+        <v>14.23419357945038</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.5987818026716797</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.2428241389819017</v>
+        <v>0.2428241390540193</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>46.4679092791263</v>
+        <v>46.46790931751328</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>10.73606056992664</v>
+        <v>10.7360605534524</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.6318077882328406</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.9944337786497428</v>
+        <v>0.9944337791030576</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>48.0184937541445</v>
+        <v>48.01849378241813</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>19.64011577984031</v>
+        <v>19.64011580312176</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.521674578412746</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.6242933303385052</v>
+        <v>0.6242933302972919</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>51.72803343672887</v>
+        <v>51.72803374604634</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>4.892172892206235</v>
+        <v>4.892172893082169</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>3.410828999694096</v>
@@ -6527,7 +6527,7 @@
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>412.8562768980707</v>
+        <v>412.8562768980706</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>78.5</v>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>46.60718705016395</v>
+        <v>46.60718701623958</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>20.28071053079523</v>
+        <v>20.28071046751299</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.3241424321894683</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.9526694864030328</v>
+        <v>-0.9526694859497032</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>51.54370683536112</v>
+        <v>51.54370701999677</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>21.88768698536685</v>
+        <v>21.88768695995172</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>7.244113267170436</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0946540648755425</v>
+        <v>0.0946540648858451</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>52.04974367339001</v>
+        <v>52.04974367596014</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>16.41710128905041</v>
+        <v>16.41710133305654</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>0.5001453202099504</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.2538401078990373</v>
+        <v>0.2538401079299498</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>53.14773007830358</v>
+        <v>53.1477300641201</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>11.76152020173603</v>
+        <v>11.76152021992988</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>0.6871457297849558</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.2012254523975209</v>
+        <v>0.201225452510844</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>51.58933289070792</v>
+        <v>51.58933262459233</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>9.458059433549581</v>
+        <v>9.458058793527998</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>0.0723271316533375</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-2.193488214128561</v>
+        <v>-2.193488204196556</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>401.1735124413433</v>
+        <v>401.1735124413417</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>7.11</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>47.12959427626178</v>
+        <v>47.12959346931158</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>24.73313625224586</v>
+        <v>24.73313633592875</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.4825239345707466</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0125307675265421</v>
+        <v>0.0125307676295716</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>54.32015029877311</v>
+        <v>54.32015030681346</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>26.59866571774237</v>
+        <v>26.59866577388376</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.4066821163780484</v>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>48.70253484587901</v>
+        <v>48.7025348256393</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>9.215489475247267</v>
+        <v>9.21548947408991</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>2.092393199534332</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.168456582777708</v>
+        <v>0.1684565827880091</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>51.42734306749836</v>
+        <v>51.42734320775916</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>18.20392818221405</v>
+        <v>18.20392821210588</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.5918397564193401</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.8599497128861151</v>
+        <v>-0.8599497137103298</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>42.09359721710171</v>
+        <v>42.09359722588825</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>21.72071838146134</v>
+        <v>21.72071838400424</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.6212137910245693</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-2.933432070483809</v>
+        <v>-2.933432070679564</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>48.26534222847655</v>
+        <v>48.26534228702744</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>22.91413234200113</v>
+        <v>22.91413233714543</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.7275578511605162</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>1.099672273896579</v>
+        <v>1.099672273793525</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>39.84062266821186</v>
+        <v>39.84062286778468</v>
       </c>
       <c r="I126" s="2" t="n">
         <v>42.94665027801086</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.5368822292223001</v>
+        <v>0.5368822282950534</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>45.83737471678543</v>
+        <v>45.83737476986276</v>
       </c>
       <c r="I127" s="2" t="n">
         <v>14.29764608553387</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.0529394249173521</v>
+        <v>0.0529394249379564</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>44.42983476818547</v>
+        <v>44.42983475725421</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>22.77973677727336</v>
+        <v>22.77973687334746</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>0.3072575363480952</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-2.034152036042409</v>
+        <v>-2.034152035527255</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>44.22690413474787</v>
+        <v>44.22690421088168</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>31.06597313548534</v>
+        <v>31.06597313854142</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.2173958519070449</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.0029887164848178</v>
+        <v>-0.0029887165260306</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>52.58486182157753</v>
+        <v>52.5848618135031</v>
       </c>
       <c r="I130" s="2" t="n">
         <v>16.46047752320021</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.1909838553125091</v>
+        <v>0.1909838553185652</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>373.1227370608756</v>
+        <v>373.1227370608755</v>
       </c>
       <c r="E131" s="2" t="n">
         <v>61.5</v>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>49.34603354371011</v>
+        <v>49.34603358625171</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>11.00222459555585</v>
+        <v>11.00222460103178</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.7467470749551198</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.3123265024027454</v>
+        <v>0.312326502052446</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>371.7519365093638</v>
+        <v>371.7519365093635</v>
       </c>
       <c r="E132" s="2" t="n">
         <v>378</v>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>37.45779824005753</v>
+        <v>37.45779825049929</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>10.50542266349597</v>
+        <v>10.50542266037648</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>0.7794784172074235</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-2.955374852460242</v>
+        <v>-2.955374852418973</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>47.20392539520287</v>
+        <v>47.20392553887792</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>5.733475215831163</v>
+        <v>5.733475259222229</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.439031728674581</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.3311641963525096</v>
+        <v>-0.3311641983100619</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
@@ -7548,10 +7548,10 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>43.38927880116792</v>
+        <v>43.38927871274372</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>8.805314801096854</v>
+        <v>8.805314763010724</v>
       </c>
       <c r="J134" s="2" t="n">
         <v>0.4128509071776405</v>
@@ -7566,7 +7566,7 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-0.0200883601133046</v>
+        <v>-0.0200883600720915</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
@@ -7601,10 +7601,10 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>41.85587268690097</v>
+        <v>41.85586850162802</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>20.63258134746982</v>
+        <v>20.63258207415718</v>
       </c>
       <c r="J135" s="2" t="n">
         <v>0.4901777989916768</v>
@@ -7619,7 +7619,7 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>0.031811319507327</v>
+        <v>0.0318113223921372</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
@@ -7654,10 +7654,10 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>52.99794127511106</v>
+        <v>52.99794124941917</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>13.02893503516588</v>
+        <v>13.02893511178756</v>
       </c>
       <c r="J136" s="2" t="n">
         <v>0.7086853104413622</v>
@@ -7672,7 +7672,7 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.1733534583424418</v>
+        <v>0.1733534584660824</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>364.7604407009598</v>
+        <v>364.7604407009597</v>
       </c>
       <c r="E137" s="2" t="n">
         <v>11.95</v>
@@ -7707,10 +7707,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>59.13099440876767</v>
+        <v>59.1309943842196</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>23.18640292490184</v>
+        <v>23.18640310114059</v>
       </c>
       <c r="J137" s="2" t="n">
         <v>0.3623921022045773</v>
@@ -7725,7 +7725,7 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.1302223385435945</v>
+        <v>0.1302223386157149</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>362.0917715694552</v>
+        <v>362.0917715694626</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>20.35</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>44.2499587159671</v>
+        <v>44.24995870288041</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>25.14902444613188</v>
+        <v>25.14902447881119</v>
       </c>
       <c r="J138" s="2" t="n">
         <v>0.2634774768903227</v>
@@ -7778,7 +7778,7 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>0.0926193732809216</v>
+        <v>0.0926193734148585</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
@@ -7813,10 +7813,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>51.57895027323431</v>
+        <v>51.57895025422862</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>5.911708053302815</v>
+        <v>5.91170785219271</v>
       </c>
       <c r="J139" s="2" t="n">
         <v>1.812958229949816</v>
@@ -7831,7 +7831,7 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>0.2017707195555352</v>
+        <v>0.2017707196070501</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>359.7762367402183</v>
+        <v>359.7762367402207</v>
       </c>
       <c r="E140" s="2" t="n">
         <v>103</v>
@@ -7866,10 +7866,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>44.5153860878924</v>
+        <v>44.51538618445012</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>20.81967094985114</v>
+        <v>20.81967089163802</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>0.2964235255700025</v>
@@ -7884,7 +7884,7 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>0.2406183789068672</v>
+        <v>0.2406183786595983</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>43.31390873631013</v>
+        <v>43.31390851093528</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>16.65434443345834</v>
+        <v>16.65434466641809</v>
       </c>
       <c r="J141" s="2" t="n">
         <v>1.016227227482118</v>
@@ -7937,7 +7937,7 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.0358365565854335</v>
+        <v>0.0358365566781607</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
@@ -7972,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>51.21504091355582</v>
+        <v>51.21504095682264</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>30.22092398403493</v>
+        <v>30.22092405952742</v>
       </c>
       <c r="J142" s="2" t="n">
         <v>0.5537829690031607</v>
@@ -7990,7 +7990,7 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-0.0817575576637551</v>
+        <v>-0.0817575576431491</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>350.6544780349945</v>
+        <v>350.6544780349947</v>
       </c>
       <c r="E143" s="2" t="n">
         <v>161</v>
@@ -8025,10 +8025,10 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>39.55753384637654</v>
+        <v>39.55753403506539</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>18.11988926100228</v>
+        <v>18.11988934130044</v>
       </c>
       <c r="J143" s="2" t="n">
         <v>0.3342551803549092</v>
@@ -8043,7 +8043,7 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>0.1039943026333256</v>
+        <v>0.1039943022211993</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>346.009195177321</v>
+        <v>346.0091951773201</v>
       </c>
       <c r="E144" s="2" t="n">
         <v>698</v>
@@ -8078,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>47.04005708151014</v>
+        <v>47.04005705793491</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>8.348994940844241</v>
+        <v>8.348994905778941</v>
       </c>
       <c r="J144" s="2" t="n">
         <v>0.324976429056467</v>
@@ -8096,7 +8096,7 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>-0.4109228346203153</v>
+        <v>-0.4109228341051416</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>53.49407444740618</v>
+        <v>53.49407457560054</v>
       </c>
       <c r="I145" s="2" t="n">
         <v>18.05380525772092</v>
@@ -8184,10 +8184,10 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>35.69395888010712</v>
+        <v>35.69395879159011</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>21.42607261756648</v>
+        <v>21.4260726483414</v>
       </c>
       <c r="J146" s="2" t="n">
         <v>0.3206128635313185</v>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>40.78431716791885</v>
+        <v>40.78431727753252</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>20.48792827391443</v>
+        <v>20.48792830866852</v>
       </c>
       <c r="J147" s="2" t="n">
         <v>0.4071510081378914</v>
@@ -8255,7 +8255,7 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>0.0296612237272985</v>
+        <v>0.0296612236551783</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
@@ -8290,10 +8290,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>50.56251113615676</v>
+        <v>50.56251120847067</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>25.93134298910724</v>
+        <v>25.93134300054706</v>
       </c>
       <c r="J148" s="2" t="n">
         <v>0.2351420323570064</v>
@@ -8308,7 +8308,7 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-0.0765711876351019</v>
+        <v>-0.0765711875526771</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v/>
       </c>
       <c r="D149" s="2" t="n">
-        <v>332.0522075482375</v>
+        <v>332.052207548237</v>
       </c>
       <c r="E149" s="2" t="n">
         <v>14.8</v>
@@ -8343,10 +8343,10 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>52.87142615185478</v>
+        <v>52.87142602450996</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>17.56150916456941</v>
+        <v>17.56150917481012</v>
       </c>
       <c r="J149" s="2" t="n">
         <v>0.665769176672532</v>
@@ -8361,7 +8361,7 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>0.1307241109445604</v>
+        <v>0.1307241110372862</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
@@ -8396,7 +8396,7 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>45.63285063743155</v>
+        <v>45.63285064604919</v>
       </c>
       <c r="I150" s="2" t="n">
         <v>18.61398452542189</v>
@@ -8414,7 +8414,7 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>-0.5718090199491005</v>
+        <v>-0.5718090199903157</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v/>
       </c>
       <c r="D151" s="2" t="n">
-        <v>324.4098094768401</v>
+        <v>324.4098094768397</v>
       </c>
       <c r="E151" s="2" t="n">
         <v>513</v>
@@ -8449,10 +8449,10 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>46.1834562312066</v>
+        <v>46.18345623996108</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>11.02633389767197</v>
+        <v>11.02633389767196</v>
       </c>
       <c r="J151" s="2" t="n">
         <v>0.5932838706177282</v>
@@ -8467,7 +8467,7 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>-5.074116119056696</v>
+        <v>-5.074116120189955</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
@@ -8502,10 +8502,10 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>48.10831040338547</v>
+        <v>48.10831046145258</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>9.16645180016965</v>
+        <v>9.166451779538887</v>
       </c>
       <c r="J152" s="2" t="n">
         <v>1.109280930033654</v>
@@ -8530,21 +8530,21 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>3629</v>
+        <v>3290</v>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>地心引力</t>
+          <t>東浦</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
         <v/>
       </c>
       <c r="D153" s="2" t="n">
-        <v>321.3872365535239</v>
+        <v>321.2478501181262</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>0</v>
+        <v>46.25</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -8555,16 +8555,16 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>39.05516882351871</v>
+        <v>38.61430823278304</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>14.92819168876053</v>
+        <v>42.11423741862148</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>0.0437134502923976</v>
+        <v>0.3909065659038184</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L153" s="2" t="n">
         <v>0</v>
@@ -8573,31 +8573,31 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>-2.305344970758014</v>
+        <v>0.3355509876244289</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>3290</v>
+        <v>3516</v>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>東浦</t>
+          <t>亞帝歐</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
         <v/>
       </c>
       <c r="D154" s="2" t="n">
-        <v>321.247850118126</v>
+        <v>320.3780805385603</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>46.25</v>
+        <v>25.1</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -8608,16 +8608,16 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>38.61430820735498</v>
+        <v>41.57158963104342</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>42.11423743333584</v>
+        <v>19.43724573560995</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0.3909065659038184</v>
+        <v>0.1056765127628301</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L154" s="2" t="n">
         <v>0</v>
@@ -8626,31 +8626,31 @@
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>0.3355509877303713</v>
+        <v>-0.06752920079692649</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>3516</v>
+        <v>3230</v>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>亞帝歐</t>
+          <t>錦明</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v/>
       </c>
       <c r="D155" s="2" t="n">
-        <v>320.3780805385603</v>
+        <v>315.331153934144</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>25.1</v>
+        <v>40.2</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -8661,16 +8661,16 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>41.57158959152186</v>
+        <v>39.68222255463586</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>19.43724570550621</v>
+        <v>21.15331626372</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.1056765127628301</v>
+        <v>1.245482279421965</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L155" s="2" t="n">
         <v>0</v>
@@ -8679,31 +8679,31 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>-0.0675292008175286</v>
+        <v>-0.2181264236544496</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>3230</v>
+        <v>3206</v>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>錦明</t>
+          <t>志豐</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
         <v/>
       </c>
       <c r="D156" s="2" t="n">
-        <v>315.3311539341441</v>
+        <v>311.4575879287574</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>40.2</v>
+        <v>34.6</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -8714,16 +8714,16 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>39.68222241974181</v>
+        <v>48.35855716242697</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>21.15331625368962</v>
+        <v>9.817544242958094</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>1.245482279421965</v>
+        <v>0.4997571661287222</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L156" s="2" t="n">
         <v>0</v>
@@ -8732,31 +8732,31 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>-0.2181264237368783</v>
+        <v>0.0287185737876893</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>3206</v>
+        <v>3526</v>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>志豐</t>
+          <t>凡甲</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v/>
       </c>
       <c r="D157" s="2" t="n">
-        <v>311.4575879287559</v>
+        <v>310.0559438993365</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>34.6</v>
+        <v>270</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -8767,13 +8767,13 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>48.35855710206596</v>
+        <v>41.34193706352144</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>9.817544212106196</v>
+        <v>36.44494499555905</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>0.4997571661287222</v>
+        <v>0.4314336617328781</v>
       </c>
       <c r="K157" s="2" t="n">
         <v>1</v>
@@ -8785,31 +8785,31 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>0.0287185738185999</v>
+        <v>0.6614459655788432</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>3526</v>
+        <v>3227</v>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>凡甲</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v/>
       </c>
       <c r="D158" s="2" t="n">
-        <v>310.0559438993365</v>
+        <v>306.6723941692638</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>270</v>
+        <v>183.5</v>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
@@ -8820,16 +8820,16 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>41.34193696849891</v>
+        <v>40.89801646856558</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>36.44494501181466</v>
+        <v>25.38867607461387</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>0.4314336617328781</v>
+        <v>0.6090715119090011</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L158" s="2" t="n">
         <v>0</v>
@@ -8838,7 +8838,7 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>0.6614459653727831</v>
+        <v>0.4226591117205718</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
@@ -8848,21 +8848,21 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>3227</v>
+        <v>3708</v>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>上緯投控</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v/>
       </c>
       <c r="D159" s="2" t="n">
-        <v>306.6723941692638</v>
+        <v>306.1316572010385</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>183.5</v>
+        <v>99.7</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -8873,16 +8873,16 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>40.89801638806037</v>
+        <v>51.80466945879562</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>25.3886760912703</v>
+        <v>18.80077031919863</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>0.6090715119090011</v>
+        <v>0.5203972432773276</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L159" s="2" t="n">
         <v>0</v>
@@ -8891,31 +8891,31 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>0.4226591117205718</v>
+        <v>0.2386846254874157</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>3708</v>
+        <v>3706</v>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>上緯投控</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v/>
       </c>
       <c r="D160" s="2" t="n">
-        <v>306.1316572010389</v>
+        <v>304.5740754238821</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>99.7</v>
+        <v>78.5</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
@@ -8926,13 +8926,13 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>51.80466920695012</v>
+        <v>31.39648460989247</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>18.80077015523207</v>
+        <v>27.97941887552145</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>0.5203972432773276</v>
+        <v>0.4061833674589742</v>
       </c>
       <c r="K160" s="2" t="n">
         <v>1</v>
@@ -8944,31 +8944,31 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>0.2386846261055992</v>
+        <v>-0.512280060532011</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>3706</v>
+        <v>3390</v>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>旭軟</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
         <v/>
       </c>
       <c r="D161" s="2" t="n">
-        <v>304.5740754238872</v>
+        <v>301.5363808200843</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>78.5</v>
+        <v>21.85</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -8979,13 +8979,13 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>31.3964841918275</v>
+        <v>46.2572385659147</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>27.9794188727052</v>
+        <v>23.95788301752827</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>0.4061833674589742</v>
+        <v>0.633836254137858</v>
       </c>
       <c r="K161" s="2" t="n">
         <v>1</v>
@@ -8997,31 +8997,31 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>-0.5122800603465407</v>
+        <v>0.0862199022434928</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>3390</v>
+        <v>3533</v>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>旭軟</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v/>
       </c>
       <c r="D162" s="2" t="n">
-        <v>301.5363808200843</v>
+        <v>292.3877120007452</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>21.85</v>
+        <v>1690</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -9032,16 +9032,16 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>46.2572385659147</v>
+        <v>51.8971291383917</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>23.95788301284617</v>
+        <v>18.58156692636146</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>0.633836254137858</v>
+        <v>1.006434342233889</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L162" s="2" t="n">
         <v>0</v>
@@ -9050,31 +9050,31 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>0.0862199022228884</v>
+        <v>23.23606975435544</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, liquidity_ok, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>3533</v>
+        <v>3556</v>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>禾瑞亞</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v/>
       </c>
       <c r="D163" s="2" t="n">
-        <v>292.3877120007452</v>
+        <v>290.4187708670108</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>1690</v>
+        <v>57.5</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -9085,16 +9085,16 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>51.89712911873224</v>
+        <v>43.26727849696328</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>18.58156698282257</v>
+        <v>23.64453494380736</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>1.006434342233889</v>
+        <v>0.3406349543769466</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L163" s="2" t="n">
         <v>0</v>
@@ -9103,31 +9103,31 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>23.23606976053725</v>
+        <v>0.1834733354709172</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, stronger_than_market</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>3556</v>
+        <v>3551</v>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>禾瑞亞</t>
+          <t>世禾</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v/>
       </c>
       <c r="D164" s="2" t="n">
-        <v>290.4187708670108</v>
+        <v>288.4625288623504</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>57.5</v>
+        <v>182.5</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -9138,16 +9138,16 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>43.26727846334602</v>
+        <v>54.26808025627501</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>23.64453495082092</v>
+        <v>11.97989740366489</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>0.3406349543769466</v>
+        <v>0.7904062940324069</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L164" s="2" t="n">
         <v>0</v>
@@ -9156,31 +9156,31 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>0.1834733354091005</v>
+        <v>1.169116030314798</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>3551</v>
+        <v>3537</v>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>世禾</t>
+          <t>堡達</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v/>
       </c>
       <c r="D165" s="2" t="n">
-        <v>288.4625288623507</v>
+        <v>288.4185606673342</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>182.5</v>
+        <v>53.2</v>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
@@ -9191,16 +9191,16 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>54.26808020892886</v>
+        <v>46.50814117145381</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>11.97989739872374</v>
+        <v>13.2755512568241</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0.7904062940324069</v>
+        <v>0.4781743917911729</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L165" s="2" t="n">
         <v>0</v>
@@ -9209,31 +9209,31 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>1.169116029799643</v>
+        <v>0.1472209433963136</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>3537</v>
+        <v>3168</v>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>堡達</t>
+          <t>眾福科</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v/>
       </c>
       <c r="D166" s="2" t="n">
-        <v>288.4185606673341</v>
+        <v>287.3397847110577</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>53.2</v>
+        <v>42.15</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -9244,16 +9244,16 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>46.50814111896543</v>
+        <v>51.38318664646331</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>13.27555127319626</v>
+        <v>12.37532031275081</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>0.4781743917911729</v>
+        <v>0.2254141711834608</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L166" s="2" t="n">
         <v>0</v>
@@ -9262,31 +9262,31 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>0.1472209433757058</v>
+        <v>0.5378699537860735</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>3168</v>
+        <v>3594</v>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>眾福科</t>
+          <t>磐儀</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v/>
       </c>
       <c r="D167" s="2" t="n">
-        <v>287.3397847110568</v>
+        <v>286.133886127168</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>42.15</v>
+        <v>46.7</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
@@ -9297,16 +9297,16 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>51.38318664874024</v>
+        <v>43.02782780292721</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>12.37532033709796</v>
+        <v>17.87816970476102</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>0.2254141711834608</v>
+        <v>0.207027264724826</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L167" s="2" t="n">
         <v>0</v>
@@ -9315,31 +9315,31 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>0.5378699537242591</v>
+        <v>0.1696961814611637</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>3594</v>
+        <v>3694</v>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>磐儀</t>
+          <t>海華</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
         <v/>
       </c>
       <c r="D168" s="2" t="n">
-        <v>286.133886127168</v>
+        <v>285.5131991137751</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>46.7</v>
+        <v>50.3</v>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
@@ -9350,16 +9350,16 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>43.02782779196419</v>
+        <v>45.57161898018442</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>17.8781697067068</v>
+        <v>18.37430624191653</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>0.207027264724826</v>
+        <v>0.454714111392245</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L168" s="2" t="n">
         <v>0</v>
@@ -9368,31 +9368,31 @@
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>0.1696961814508633</v>
+        <v>0.3515741288856315</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>3694</v>
+        <v>3135</v>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>海華</t>
+          <t>凌航</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
         <v/>
       </c>
       <c r="D169" s="2" t="n">
-        <v>285.5131991137752</v>
+        <v>284.9418303270119</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>50.3</v>
+        <v>156.5</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
@@ -9403,16 +9403,16 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>45.57161886261898</v>
+        <v>38.78436838619973</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>18.37430624974769</v>
+        <v>11.52867015023618</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0.454714111392245</v>
+        <v>0.7373651866710851</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L169" s="2" t="n">
         <v>0</v>
@@ -9421,31 +9421,31 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>0.3515741289268475</v>
+        <v>-1.170619091525329</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>3135</v>
+        <v>3322</v>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>凌航</t>
+          <t>建舜電</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
         <v/>
       </c>
       <c r="D170" s="2" t="n">
-        <v>284.9418303270119</v>
+        <v>284.3930938783531</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>156.5</v>
+        <v>11.1</v>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
@@ -9456,16 +9456,16 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>38.78436836582654</v>
+        <v>49.19138894100186</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>11.52867015023618</v>
+        <v>13.55275131135225</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>0.7373651866710851</v>
+        <v>0.5420062022786005</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L170" s="2" t="n">
         <v>0</v>
@@ -9474,31 +9474,31 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-1.170619091484121</v>
+        <v>0.0666244622904473</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>3322</v>
+        <v>3701</v>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>建舜電</t>
+          <t>大眾控</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v/>
       </c>
       <c r="D171" s="2" t="n">
-        <v>284.3930938783531</v>
+        <v>279.1952278226266</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>11.1</v>
+        <v>41.25</v>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
@@ -9509,16 +9509,16 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>49.19138889180918</v>
+        <v>50.96296186173326</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>13.55275131583248</v>
+        <v>16.74922172477383</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>0.5420062022786005</v>
+        <v>0.3333917647610592</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L171" s="2" t="n">
         <v>0</v>
@@ -9527,31 +9527,31 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>0.0666244620431781</v>
+        <v>0.102656366400652</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, stronger_than_market, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>3701</v>
+        <v>3704</v>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>大眾控</t>
+          <t>合勤控</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v/>
       </c>
       <c r="D172" s="2" t="n">
-        <v>279.1952278226281</v>
+        <v>277.8900781124393</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>41.25</v>
+        <v>40.5</v>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
@@ -9562,13 +9562,13 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>50.96296183014022</v>
+        <v>46.23541351223167</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>16.74922170737064</v>
+        <v>14.27112281273554</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>0.3333917647610592</v>
+        <v>0.384194537522191</v>
       </c>
       <c r="K172" s="2" t="n">
         <v>0</v>
@@ -9580,31 +9580,31 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>0.1026563664418655</v>
+        <v>0.2161877449307915</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>3704</v>
+        <v>4106</v>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>合勤控</t>
+          <t>雃博</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
         <v/>
       </c>
       <c r="D173" s="2" t="n">
-        <v>277.8900781124393</v>
+        <v>268.8442270146386</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>40.5</v>
+        <v>24.2</v>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
@@ -9615,13 +9615,13 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>46.2354135607258</v>
+        <v>42.03105099446837</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>14.2711228057498</v>
+        <v>11.23120578988346</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>0.384194537522191</v>
+        <v>0.9657117260534932</v>
       </c>
       <c r="K173" s="2" t="n">
         <v>0</v>
@@ -9633,31 +9633,31 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>0.2161877448483692</v>
+        <v>-0.0220059604740787</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>4106</v>
+        <v>3438</v>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>雃博</t>
+          <t>類比科</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
         <v/>
       </c>
       <c r="D174" s="2" t="n">
-        <v>268.8442270146386</v>
+        <v>266.1375672786276</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>24.2</v>
+        <v>61.1</v>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
@@ -9668,16 +9668,16 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>42.03105134648935</v>
+        <v>46.88013320185718</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>11.23120564382259</v>
+        <v>16.42968032334678</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>0.9657117260534932</v>
+        <v>0.5575251084374677</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L174" s="2" t="n">
         <v>0</v>
@@ -9686,31 +9686,31 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-0.0220059605874139</v>
+        <v>-0.2668556483850831</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>3438</v>
+        <v>3709</v>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>類比科</t>
+          <t>鑫聯大投控</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
         <v/>
       </c>
       <c r="D175" s="2" t="n">
-        <v>266.1375672786276</v>
+        <v>265.873832845751</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>61.1</v>
+        <v>63.1</v>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
@@ -9721,16 +9721,16 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>46.8801332048136</v>
+        <v>39.61134419480405</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>16.42968030492973</v>
+        <v>31.78151449908198</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>0.5575251084374677</v>
+        <v>0.2911042501545425</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L175" s="2" t="n">
         <v>0</v>
@@ -9739,31 +9739,31 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>-0.2668556484571978</v>
+        <v>0.3654463287349392</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>3709</v>
+        <v>3213</v>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>鑫聯大投控</t>
+          <t>茂訊</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
         <v/>
       </c>
       <c r="D176" s="2" t="n">
-        <v>265.8738328457508</v>
+        <v>265.6628096021356</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>63.1</v>
+        <v>124.5</v>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
@@ -9774,16 +9774,16 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>39.61134423826611</v>
+        <v>47.04086510003325</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>31.781514502922</v>
+        <v>8.371803217059307</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>0.2911042501545425</v>
+        <v>0.3864822905953792</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L176" s="2" t="n">
         <v>0</v>
@@ -9792,31 +9792,31 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>0.3654463285906995</v>
+        <v>0.2610426487560247</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>3213</v>
+        <v>4108</v>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>茂訊</t>
+          <t>懷特</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
         <v/>
       </c>
       <c r="D177" s="2" t="n">
-        <v>265.6628096021356</v>
+        <v>263.2922202440541</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>124.5</v>
+        <v>11.45</v>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
@@ -9827,16 +9827,16 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>47.04086521062425</v>
+        <v>51.62764091334794</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>8.371803113348037</v>
+        <v>35.38701422269337</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>0.3864822905953792</v>
+        <v>0.4192700410840189</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L177" s="2" t="n">
         <v>0</v>
@@ -9845,31 +9845,31 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>0.2610426476227068</v>
+        <v>0.02544579615727</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>4108</v>
+        <v>3515</v>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>懷特</t>
+          <t>華擎</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
         <v/>
       </c>
       <c r="D178" s="2" t="n">
-        <v>263.2922202440541</v>
+        <v>263.1139468326348</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>11.45</v>
+        <v>211</v>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
@@ -9880,13 +9880,13 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>51.62764092932082</v>
+        <v>45.70941917809253</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>35.38701418578237</v>
+        <v>14.49515801629096</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>0.4192700410840189</v>
+        <v>0.2552239948841377</v>
       </c>
       <c r="K178" s="2" t="n">
         <v>0</v>
@@ -9898,31 +9898,31 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>0.025445796126361</v>
+        <v>-0.6171027855892541</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>3515</v>
+        <v>3687</v>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>華擎</t>
+          <t>歐買尬</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v/>
       </c>
       <c r="D179" s="2" t="n">
-        <v>263.1139468326348</v>
+        <v>261.5049683288456</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>211</v>
+        <v>60.3</v>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
@@ -9933,16 +9933,16 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>45.70941879396094</v>
+        <v>28.13757289255188</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>14.49515792844758</v>
+        <v>19.41471890936596</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>0.2552239948841377</v>
+        <v>1.070798334939756</v>
       </c>
       <c r="K179" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L179" s="2" t="n">
         <v>0</v>
@@ -9951,31 +9951,31 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>-0.6171027836316874</v>
+        <v>0.0560125500619221</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>3687</v>
+        <v>3629</v>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>歐買尬</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
         <v/>
       </c>
       <c r="D180" s="2" t="n">
-        <v>261.5049683288457</v>
+        <v>261.3872365535239</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>60.3</v>
+        <v>0</v>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
@@ -9986,16 +9986,16 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>28.1375730542245</v>
+        <v>39.05516881974161</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>19.41471886241182</v>
+        <v>14.9281916681353</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>1.070798334939756</v>
+        <v>0.0437134502923976</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L180" s="2" t="n">
         <v>0</v>
@@ -10004,11 +10004,11 @@
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>0.0560125496704095</v>
+        <v>-2.305344970139839</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -10039,10 +10039,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>47.60838333064537</v>
+        <v>47.608383124118</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>10.0192533680232</v>
+        <v>10.01925375999575</v>
       </c>
       <c r="J181" s="2" t="n">
         <v>0.7850988528511064</v>
@@ -10057,7 +10057,7 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>0.4903637964348044</v>
+        <v>0.4903637979802566</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v/>
       </c>
       <c r="D182" s="2" t="n">
-        <v>255.7815133847023</v>
+        <v>255.7815133847074</v>
       </c>
       <c r="E182" s="2" t="n">
         <v>104</v>
@@ -10092,7 +10092,7 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>48.63296647615083</v>
+        <v>48.63296647852606</v>
       </c>
       <c r="I182" s="2" t="n">
         <v>10.21380099512586</v>
@@ -10110,7 +10110,7 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>0.88903404316512</v>
+        <v>0.8890340431754229</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v/>
       </c>
       <c r="D183" s="2" t="n">
-        <v>254.381914556514</v>
+        <v>254.3819145565139</v>
       </c>
       <c r="E183" s="2" t="n">
         <v>653</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>41.77346197884273</v>
+        <v>41.77346198694138</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>16.17258416861846</v>
+        <v>16.17258419120375</v>
       </c>
       <c r="J183" s="2" t="n">
         <v>0.4335019514652792</v>
@@ -10163,7 +10163,7 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>-4.713779670573313</v>
+        <v>-4.71377967088241</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v/>
       </c>
       <c r="D184" s="2" t="n">
-        <v>250.0304092107276</v>
+        <v>250.0304092107275</v>
       </c>
       <c r="E184" s="2" t="n">
         <v>19.75</v>
@@ -10198,7 +10198,7 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>47.39636178109754</v>
+        <v>47.39636172511529</v>
       </c>
       <c r="I184" s="2" t="n">
         <v>18.24161561824787</v>
@@ -10216,7 +10216,7 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>0.0310787336020975</v>
+        <v>0.0310787336536124</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v/>
       </c>
       <c r="D185" s="2" t="n">
-        <v>249.9094847718252</v>
+        <v>249.9094847718254</v>
       </c>
       <c r="E185" s="2" t="n">
         <v>27.3</v>
@@ -10251,10 +10251,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>44.64834206252901</v>
+        <v>44.6483421447281</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>17.91381504925493</v>
+        <v>17.91381507185823</v>
       </c>
       <c r="J185" s="2" t="n">
         <v>0.7684671936753076</v>
@@ -10269,7 +10269,7 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>0.0629134418753122</v>
+        <v>0.062913441772282</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v/>
       </c>
       <c r="D186" s="2" t="n">
-        <v>243.9432647290011</v>
+        <v>243.9432647290009</v>
       </c>
       <c r="E186" s="2" t="n">
         <v>19.9</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>34.58677221525839</v>
+        <v>34.58677267594727</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>35.69659074258634</v>
+        <v>35.6965907854936</v>
       </c>
       <c r="J186" s="2" t="n">
         <v>0.1934081488626786</v>
@@ -10322,7 +10322,7 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>-0.1212948783001399</v>
+        <v>-0.1212948784237782</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v/>
       </c>
       <c r="D187" s="2" t="n">
-        <v>237.9375676171883</v>
+        <v>237.9375676171884</v>
       </c>
       <c r="E187" s="2" t="n">
         <v>19.25</v>
@@ -10357,7 +10357,7 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>43.59365348306589</v>
+        <v>43.59365322687039</v>
       </c>
       <c r="I187" s="2" t="n">
         <v>17.10958421274027</v>
@@ -10375,7 +10375,7 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>0.0218602289759203</v>
+        <v>0.021860229048042</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v/>
       </c>
       <c r="D188" s="2" t="n">
-        <v>235.048368383881</v>
+        <v>235.0483683838806</v>
       </c>
       <c r="E188" s="2" t="n">
         <v>652</v>
@@ -10410,10 +10410,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>47.27195609771123</v>
+        <v>47.27195609423827</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>19.26413918561037</v>
+        <v>19.26413927474908</v>
       </c>
       <c r="J188" s="2" t="n">
         <v>0.3624515946954439</v>
@@ -10428,7 +10428,7 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>-10.19451845685668</v>
+        <v>-10.19451845726875</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v/>
       </c>
       <c r="D189" s="2" t="n">
-        <v>230.8275566718125</v>
+        <v>230.8275566718126</v>
       </c>
       <c r="E189" s="2" t="n">
         <v>31.9</v>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>34.84288350546984</v>
+        <v>34.8428833703129</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>23.0436834346266</v>
+        <v>23.04368344334643</v>
       </c>
       <c r="J189" s="2" t="n">
         <v>0.5282416522659487</v>
@@ -10481,7 +10481,7 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>-0.06317739051467459</v>
+        <v>-0.0631773903292238</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
@@ -10516,10 +10516,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>46.77426941486116</v>
+        <v>46.77426936214098</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>13.73828777303626</v>
+        <v>13.73828789791971</v>
       </c>
       <c r="J190" s="2" t="n">
         <v>0.2591908265976749</v>
@@ -10534,7 +10534,7 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>-0.0075714737975519</v>
+        <v>-0.0075714736945244</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v/>
       </c>
       <c r="D191" s="2" t="n">
-        <v>226.0108429391079</v>
+        <v>226.0108429391082</v>
       </c>
       <c r="E191" s="2" t="n">
         <v>14.6</v>
@@ -10569,10 +10569,10 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>50.93390952116678</v>
+        <v>50.93390951603405</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>25.5422944043066</v>
+        <v>25.54229446200077</v>
       </c>
       <c r="J191" s="2" t="n">
         <v>1.140393766398325</v>
@@ -10587,7 +10587,7 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>0.3277367146826626</v>
+        <v>0.3277367147032692</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v/>
       </c>
       <c r="D192" s="2" t="n">
-        <v>220.8366424488547</v>
+        <v>220.8366424488549</v>
       </c>
       <c r="E192" s="2" t="n">
         <v>14</v>
@@ -10622,10 +10622,10 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>38.65705422368265</v>
+        <v>38.65705426897056</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>14.91962117887566</v>
+        <v>14.91962117223156</v>
       </c>
       <c r="J192" s="2" t="n">
         <v>0.08958135705464371</v>
@@ -10640,7 +10640,7 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>-0.0224784325815746</v>
+        <v>-0.0224784325918771</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v/>
       </c>
       <c r="D193" s="2" t="n">
-        <v>219.8242724282754</v>
+        <v>219.8242724282755</v>
       </c>
       <c r="E193" s="2" t="n">
         <v>10.5</v>
@@ -10675,10 +10675,10 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>44.16630753387545</v>
+        <v>44.16630739271048</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>33.65499033617413</v>
+        <v>33.65499039261265</v>
       </c>
       <c r="J193" s="2" t="n">
         <v>0.2794921370641668</v>
@@ -10693,7 +10693,7 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>-0.0300961401502761</v>
+        <v>-0.0300961401090633</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v/>
       </c>
       <c r="D194" s="2" t="n">
-        <v>215.5818471401694</v>
+        <v>215.5818471401686</v>
       </c>
       <c r="E194" s="2" t="n">
         <v>58.3</v>
@@ -10728,10 +10728,10 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>52.31353241950588</v>
+        <v>52.31353247425698</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>17.71037292416205</v>
+        <v>17.71037293625317</v>
       </c>
       <c r="J194" s="2" t="n">
         <v>0.5675688184263168</v>
@@ -10746,7 +10746,7 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>0.1825992712268265</v>
+        <v>0.1825992712062227</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v/>
       </c>
       <c r="D195" s="2" t="n">
-        <v>214.9219248483568</v>
+        <v>214.9219248483569</v>
       </c>
       <c r="E195" s="2" t="n">
         <v>35.2</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>43.40730771616023</v>
+        <v>43.40730773649717</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>14.61515330981258</v>
+        <v>14.61515335188473</v>
       </c>
       <c r="J195" s="2" t="n">
         <v>0.467855320986675</v>
@@ -10799,7 +10799,7 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>-0.1901915743965998</v>
+        <v>-0.1901915743862998</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v/>
       </c>
       <c r="D196" s="2" t="n">
-        <v>210.0841015446433</v>
+        <v>210.0841015446434</v>
       </c>
       <c r="E196" s="2" t="n">
         <v>51</v>
@@ -10834,10 +10834,10 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>52.56529865776917</v>
+        <v>52.56529868475364</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>14.06841845287798</v>
+        <v>14.06841846391618</v>
       </c>
       <c r="J196" s="2" t="n">
         <v>0.5421491004646335</v>
@@ -10852,7 +10852,7 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>0.1965699216243325</v>
+        <v>0.1965699218303901</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>46.58338784143464</v>
+        <v>46.58338787905806</v>
       </c>
       <c r="I197" s="2" t="n">
         <v>11.28692572734666</v>
@@ -10905,7 +10905,7 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>0.953971488626174</v>
+        <v>0.9539714881934492</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>38.52468732332654</v>
+        <v>38.52468738492916</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>37.05643639370078</v>
+        <v>37.05643639838571</v>
       </c>
       <c r="J198" s="2" t="n">
         <v>0.2184035076860174</v>
@@ -10958,7 +10958,7 @@
         <v>-1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>0.6704926592224028</v>
+        <v>0.6704926587072642</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
@@ -10993,10 +10993,10 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>38.22585978676882</v>
+        <v>38.22585984792831</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>23.83100220409703</v>
+        <v>23.83100221008213</v>
       </c>
       <c r="J199" s="2" t="n">
         <v>0.2853829753307409</v>
@@ -11011,7 +11011,7 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>-2.112349116211628</v>
+        <v>-2.11234911724192</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
@@ -11046,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>31.95778412479149</v>
+        <v>31.95778432370442</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>15.63401049780533</v>
+        <v>15.63401047274968</v>
       </c>
       <c r="J200" s="2" t="n">
         <v>1.196010165141951</v>
@@ -11064,7 +11064,7 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>-0.0902748370536135</v>
+        <v>-0.0902748370948242</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v/>
       </c>
       <c r="D201" s="2" t="n">
-        <v>195.7109791899733</v>
+        <v>195.7109791899732</v>
       </c>
       <c r="E201" s="2" t="n">
         <v>77.09999999999999</v>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>44.11258731593635</v>
+        <v>44.11258736805052</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>14.53794899433566</v>
+        <v>14.53794902951426</v>
       </c>
       <c r="J201" s="2" t="n">
         <v>0.4063902882826609</v>
@@ -11152,10 +11152,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>29.84643062569104</v>
+        <v>29.84643053458743</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>58.07450583907134</v>
+        <v>58.0745059067189</v>
       </c>
       <c r="J202" s="2" t="n">
         <v>0.4905875454765599</v>
@@ -11170,7 +11170,7 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>0.5493708900905903</v>
+        <v>0.5493708902966441</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
@@ -11205,10 +11205,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>33.17251755388668</v>
+        <v>33.17251754521899</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>28.56067902483281</v>
+        <v>28.56067908889364</v>
       </c>
       <c r="J203" s="2" t="n">
         <v>0.4792301118158766</v>
@@ -11223,7 +11223,7 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>0.0621842436634878</v>
+        <v>0.0621842437768132</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>45.37750877044335</v>
+        <v>45.37750872380226</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>11.75752674102634</v>
+        <v>11.7575266860422</v>
       </c>
       <c r="J204" s="2" t="n">
         <v>0.8808588173468305</v>
@@ -11276,7 +11276,7 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>-0.07907613770497721</v>
+        <v>-0.07907613749895789</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
@@ -11311,10 +11311,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>29.0172209318125</v>
+        <v>29.01722089929555</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>30.21850635688993</v>
+        <v>30.21850639642134</v>
       </c>
       <c r="J205" s="2" t="n">
         <v>0.5652406291312982</v>
@@ -11329,7 +11329,7 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>-0.2617420104770629</v>
+        <v>-0.2617420104152437</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v/>
       </c>
       <c r="D206" s="2" t="n">
-        <v>182.3726822288272</v>
+        <v>182.3726822288274</v>
       </c>
       <c r="E206" s="2" t="n">
         <v>110.5</v>
@@ -11364,10 +11364,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>50.72930175891121</v>
+        <v>50.72930171640248</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>13.7788118795389</v>
+        <v>13.77881192339523</v>
       </c>
       <c r="J206" s="2" t="n">
         <v>0.3830540577101557</v>
@@ -11382,7 +11382,7 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>-0.0980952676674125</v>
+        <v>-0.09809526702862841</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
@@ -11417,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>34.64399084587464</v>
+        <v>34.64399070597013</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>17.09337357855713</v>
+        <v>17.09337361624689</v>
       </c>
       <c r="J207" s="2" t="n">
         <v>0.3982888792338676</v>
@@ -11435,7 +11435,7 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-0.0332885155880213</v>
+        <v>-0.0332885153613569</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
@@ -11470,10 +11470,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>39.39771037392239</v>
+        <v>39.39771049208377</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>16.33067011514816</v>
+        <v>16.33067010170964</v>
       </c>
       <c r="J208" s="2" t="n">
         <v>0.7955577684178937</v>
@@ -11488,7 +11488,7 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>0.08360429941967661</v>
+        <v>0.08360429946088779</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
@@ -11523,10 +11523,10 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>41.16931264060453</v>
+        <v>41.16931276059569</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>22.96575192336523</v>
+        <v>22.96575194606943</v>
       </c>
       <c r="J209" s="2" t="n">
         <v>0.1180651104121889</v>
@@ -11541,7 +11541,7 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>0.342491663142044</v>
+        <v>0.3424916631626451</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>47.89640033981435</v>
+        <v>47.89640022451787</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>17.86092189821939</v>
+        <v>17.86092190742775</v>
       </c>
       <c r="J210" s="2" t="n">
         <v>0.4043678615126545</v>
@@ -11594,7 +11594,7 @@
         <v>-1</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>0.1370978238611596</v>
+        <v>0.1370978238714602</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
@@ -11629,10 +11629,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>44.37292991258632</v>
+        <v>44.37292994748754</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>19.10381808059683</v>
+        <v>19.1038180430056</v>
       </c>
       <c r="J211" s="2" t="n">
         <v>0.6497971648231401</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>0.7238090896883058</v>
+        <v>0.7238090895852611</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>46.67326755309348</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>17.53420183281143</v>
+        <v>17.53420184259065</v>
       </c>
       <c r="J212" s="2" t="n">
         <v>0.2835473786635566</v>
@@ -11721,7 +11721,7 @@
         <v/>
       </c>
       <c r="D213" s="2" t="n">
-        <v>137.4314706466344</v>
+        <v>137.4314706466339</v>
       </c>
       <c r="E213" s="2" t="n">
         <v>68.3</v>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>49.73196177911577</v>
+        <v>49.73196170669712</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>14.11397451180171</v>
+        <v>14.11397463581732</v>
       </c>
       <c r="J213" s="2" t="n">
         <v>0.5047933977906637</v>
@@ -11753,7 +11753,7 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>-0.015025161054903</v>
+        <v>-0.0150251607458176</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v/>
       </c>
       <c r="D214" s="2" t="n">
-        <v>137.2380145251094</v>
+        <v>137.2380145251097</v>
       </c>
       <c r="E214" s="2" t="n">
         <v>22.85</v>
@@ -11788,10 +11788,10 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>35.20521632402517</v>
+        <v>35.20521621067009</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>12.04151664213782</v>
+        <v>12.04151699505592</v>
       </c>
       <c r="J214" s="2" t="n">
         <v>1.421691718403457</v>
@@ -11806,7 +11806,7 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>-0.0141270206757264</v>
+        <v>-0.0141270205211844</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v/>
       </c>
       <c r="D215" s="2" t="n">
-        <v>129.4026749030053</v>
+        <v>129.4026749030052</v>
       </c>
       <c r="E215" s="2" t="n">
         <v>14.95</v>
@@ -11841,7 +11841,7 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>48.84424320511082</v>
+        <v>48.84424561302122</v>
       </c>
       <c r="I215" s="2" t="n">
         <v>15.94753029499698</v>
@@ -11894,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>49.0437828197308</v>
+        <v>49.04378282547003</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>19.74189416567812</v>
+        <v>19.74189416567811</v>
       </c>
       <c r="J216" s="2" t="n">
         <v>0.1384763513731558</v>
@@ -11912,7 +11912,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>-0.0527104474309124</v>
+        <v>-0.052710447327883</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -11947,10 +11947,10 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>40.61371748400847</v>
+        <v>40.61371756671651</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>11.21686481607062</v>
+        <v>11.21686480633752</v>
       </c>
       <c r="J217" s="2" t="n">
         <v>0.2582770506607649</v>
@@ -11965,7 +11965,7 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>0.1110412916758103</v>
+        <v>0.1110412917479304</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -12000,10 +12000,10 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>46.29663029706939</v>
+        <v>46.29663027208385</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>16.4708905136288</v>
+        <v>16.47089058207355</v>
       </c>
       <c r="J218" s="2" t="n">
         <v>0.3801791620712966</v>
@@ -12018,7 +12018,7 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>0.1840721635738653</v>
+        <v>0.1840721636871898</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
@@ -12053,10 +12053,10 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>37.54012138369113</v>
+        <v>37.54012114014884</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>12.07796395094158</v>
+        <v>12.07796392364952</v>
       </c>
       <c r="J219" s="2" t="n">
         <v>0.3130017307264982</v>
@@ -12071,7 +12071,7 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>-0.010365256890316</v>
+        <v>-0.0103652568078903</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v/>
       </c>
       <c r="D220" s="2" t="n">
-        <v>94.96559799731692</v>
+        <v>94.96559799732042</v>
       </c>
       <c r="E220" s="2" t="n">
         <v>11.8</v>
@@ -12106,10 +12106,10 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>40.0114330135693</v>
+        <v>40.01143225300314</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>14.80551845332079</v>
+        <v>14.80551809012956</v>
       </c>
       <c r="J220" s="2" t="n">
         <v>0.2498481353990211</v>
@@ -12124,7 +12124,7 @@
         <v>-1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>-0.0240196440860752</v>
+        <v>-0.0240196438491088</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>50.25773208751729</v>
+        <v>50.25773205207906</v>
       </c>
       <c r="I221" s="2" t="n">
         <v>14.16688044040262</v>
@@ -12177,7 +12177,7 @@
         <v>-1</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>0.3190265751597607</v>
+        <v>0.3190265752215814</v>
       </c>
       <c r="O221" s="2" t="inlineStr">
         <is>
@@ -12212,10 +12212,10 @@
         <v>0</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>43.04862200712677</v>
+        <v>43.04862166754791</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>10.36997582240019</v>
+        <v>10.36997594025252</v>
       </c>
       <c r="J222" s="2" t="n">
         <v>0.5073702856040477</v>
@@ -12230,7 +12230,7 @@
         <v>-1</v>
       </c>
       <c r="N222" s="2" t="n">
-        <v>0.0136539160658655</v>
+        <v>0.0136539161585887</v>
       </c>
       <c r="O222" s="2" t="inlineStr">
         <is>
@@ -12265,10 +12265,10 @@
         <v>0</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>44.11909459770234</v>
+        <v>44.11909462483294</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>12.5187331923084</v>
+        <v>12.51873316392325</v>
       </c>
       <c r="J223" s="2" t="n">
         <v>0.9613365516793488</v>
@@ -12283,7 +12283,7 @@
         <v>-1</v>
       </c>
       <c r="N223" s="2" t="n">
-        <v>0.0393229268417778</v>
+        <v>0.039322926821171</v>
       </c>
       <c r="O223" s="2" t="inlineStr">
         <is>
@@ -12304,7 +12304,7 @@
         <v/>
       </c>
       <c r="D224" s="2" t="n">
-        <v>74.85521857823937</v>
+        <v>74.85521857823912</v>
       </c>
       <c r="E224" s="2" t="n">
         <v>48.7</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="H224" s="2" t="n">
-        <v>46.96525060736594</v>
+        <v>46.96525075073376</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>15.5830130374488</v>
+        <v>15.58301305034657</v>
       </c>
       <c r="J224" s="2" t="n">
         <v>0.3781150598065702</v>
@@ -12336,7 +12336,7 @@
         <v>-1</v>
       </c>
       <c r="N224" s="2" t="n">
-        <v>0.3319642135526592</v>
+        <v>0.3319642134908434</v>
       </c>
       <c r="O224" s="2" t="inlineStr">
         <is>
@@ -12371,10 +12371,10 @@
         <v>0</v>
       </c>
       <c r="H225" s="2" t="n">
-        <v>45.70343860260826</v>
+        <v>45.70343865428038</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>19.20010533553647</v>
+        <v>19.20010531014862</v>
       </c>
       <c r="J225" s="2" t="n">
         <v>1.055784627332064</v>
@@ -12389,7 +12389,7 @@
         <v>-1</v>
       </c>
       <c r="N225" s="2" t="n">
-        <v>0.0591181191247662</v>
+        <v>0.0591181191671453</v>
       </c>
       <c r="O225" s="2" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v/>
       </c>
       <c r="D226" s="2" t="n">
-        <v>56.85602446758466</v>
+        <v>56.85602446759344</v>
       </c>
       <c r="E226" s="2" t="n">
         <v>27.85</v>
@@ -12424,10 +12424,10 @@
         <v>0</v>
       </c>
       <c r="H226" s="2" t="n">
-        <v>43.86931001681197</v>
+        <v>43.86931034852221</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>18.13334868728202</v>
+        <v>18.13334872818614</v>
       </c>
       <c r="J226" s="2" t="n">
         <v>0.4345678402509355</v>
@@ -12442,7 +12442,7 @@
         <v>-1</v>
       </c>
       <c r="N226" s="2" t="n">
-        <v>0.1599528790481303</v>
+        <v>0.1599528785845019</v>
       </c>
       <c r="O226" s="2" t="inlineStr">
         <is>

--- a/output/full_scan/batch_seq4_2026-09-24.xlsx
+++ b/output/full_scan/batch_seq4_2026-09-24.xlsx
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>73.61262511635334</v>
+        <v>73.61262511702903</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>20.01966497108525</v>
+        <v>20.01966502680879</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>2.256065661144051</v>
@@ -570,7 +570,7 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>53.07681500991646</v>
+        <v>53.07681501214108</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
@@ -605,10 +605,10 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>67.03687083488224</v>
+        <v>67.03687082234694</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>21.50678527587094</v>
+        <v>21.50678525865914</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>2.552686156311622</v>
@@ -623,7 +623,7 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>6.515014567438964</v>
+        <v>6.515014567550206</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
@@ -658,10 +658,10 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>66.1269640827113</v>
+        <v>66.1269640814337</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>15.2146541959244</v>
+        <v>15.21465421327565</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>2.168171616729074</v>
@@ -711,10 +711,10 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>72.16689468558531</v>
+        <v>72.16689468078512</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>33.88548433928054</v>
+        <v>33.88548430518981</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>5.123988169742399</v>
@@ -729,7 +729,7 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.323714667351038</v>
+        <v>0.3237146674066748</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
@@ -764,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>76.24830779956694</v>
+        <v>76.24830783011018</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>38.37873979978102</v>
+        <v>38.3787398026775</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>1.680779748390488</v>
@@ -782,7 +782,7 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>2.145270549690713</v>
+        <v>2.145270549746336</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>70.62770706635015</v>
+        <v>70.62770706931141</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>34.81472244938559</v>
+        <v>34.81472243700249</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>2.179618110693879</v>
@@ -835,7 +835,7 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>2.560568943982957</v>
+        <v>2.560568943715896</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>67.11364208435876</v>
+        <v>67.11364208190268</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>14.8457479161741</v>
+        <v>14.84574792497125</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>0.5958135246986367</v>
@@ -888,7 +888,7 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>9.768803596050692</v>
+        <v>9.768803595828135</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>64.68574495859956</v>
+        <v>64.68574497750606</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>41.79902486126949</v>
+        <v>41.79902479055165</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>1.121416808824015</v>
@@ -941,7 +941,7 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.3913441599161977</v>
+        <v>-0.3913441597492895</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>67.87454425978945</v>
+        <v>67.87454424671682</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>15.5475867926993</v>
+        <v>15.54758684414662</v>
       </c>
       <c r="J10" s="2" t="n">
         <v>2.442862612192605</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>10.20235694896888</v>
+        <v>10.20235694785615</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1002.464051269198</v>
+        <v>1002.464051269199</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>949</v>
@@ -1029,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>64.77022451671013</v>
+        <v>64.77022453204088</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>18.76797480187767</v>
+        <v>18.76797485460678</v>
       </c>
       <c r="J11" s="2" t="n">
         <v>1.55740912058492</v>
@@ -1047,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>5.493597246406473</v>
+        <v>5.493597245627541</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>63.0883358184707</v>
+        <v>63.08833580733247</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>28.27049494704369</v>
+        <v>28.27049494780662</v>
       </c>
       <c r="J12" s="2" t="n">
         <v>8.535996842204639</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.670598970757676</v>
+        <v>1.67059897088008</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>70.54873041751648</v>
+        <v>70.54873041339124</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>30.03639121069384</v>
+        <v>30.03639120017828</v>
       </c>
       <c r="J13" s="2" t="n">
         <v>4.15590278049895</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1.176275938393974</v>
+        <v>1.176275938371723</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>58.82916732694565</v>
+        <v>58.8291673289619</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>13.03647504196318</v>
+        <v>13.0364751645359</v>
       </c>
       <c r="J14" s="2" t="n">
         <v>2.271120992378672</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.9251346844667624</v>
+        <v>0.9251346846003012</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>948.395099699998</v>
+        <v>948.3950996999982</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>183.5</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>79.53511601217886</v>
+        <v>79.53511601833114</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>40.6413145821616</v>
+        <v>40.64131463136154</v>
       </c>
       <c r="J15" s="2" t="n">
         <v>0.6882891185080461</v>
@@ -1259,7 +1259,7 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>5.219078931608834</v>
+        <v>5.219078931831397</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>73.32995744759307</v>
+        <v>73.32995745918355</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>32.55063785441009</v>
+        <v>32.55063781552636</v>
       </c>
       <c r="J16" s="2" t="n">
         <v>1.362680603084347</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>21.84465127099004</v>
+        <v>21.84465127143505</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>59.94634976631204</v>
+        <v>59.94634972327464</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>26.18344514914594</v>
+        <v>26.18344527626657</v>
       </c>
       <c r="J17" s="2" t="n">
         <v>1.817767666721637</v>
@@ -1365,7 +1365,7 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.2098499129823237</v>
+        <v>0.2098499131269788</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>62.60176723243313</v>
+        <v>62.60176724322792</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>17.75894016691775</v>
+        <v>17.75894017279126</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>4.039062964988273</v>
@@ -1418,7 +1418,7 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.1722564124937922</v>
+        <v>0.1722564124804394</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>887.6241606126425</v>
+        <v>887.6241606126426</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>117.5</v>
@@ -1453,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>64.07434281064116</v>
+        <v>64.07434276501203</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>17.01398457651544</v>
+        <v>17.01398461589568</v>
       </c>
       <c r="J19" s="2" t="n">
         <v>0.88347853808003</v>
@@ -1471,7 +1471,7 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.531836508738802</v>
+        <v>1.531836508939085</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>68.84309065202456</v>
+        <v>68.84309057979505</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>18.39980672384296</v>
+        <v>18.39980668087275</v>
       </c>
       <c r="J20" s="2" t="n">
         <v>3.85118759147017</v>
@@ -1524,7 +1524,7 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.43108627425687</v>
+        <v>1.431086274535054</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1559,10 +1559,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>63.57934130478261</v>
+        <v>63.57934130034304</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>32.01222402240474</v>
+        <v>32.01222399340288</v>
       </c>
       <c r="J21" s="2" t="n">
         <v>0.6301988159388836</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>2.033912041420969</v>
+        <v>2.033912041443251</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>832.9882605574228</v>
+        <v>832.9882605574229</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>2340</v>
@@ -1612,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>60.7141556281677</v>
+        <v>60.71415560075543</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>15.67230250217718</v>
+        <v>15.67230245129389</v>
       </c>
       <c r="J22" s="2" t="n">
         <v>1.36882934122329</v>
@@ -1630,7 +1630,7 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>40.89732102316363</v>
+        <v>40.89732103095264</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>831.8608200404157</v>
+        <v>831.8608200404159</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>28.3</v>
@@ -1665,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>72.74114423215178</v>
+        <v>72.74114422245343</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>52.07465052285972</v>
+        <v>52.07465055784497</v>
       </c>
       <c r="J23" s="2" t="n">
         <v>0.4287690140134053</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.1286372873003842</v>
+        <v>0.1286372873671482</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1718,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>58.21834527532604</v>
+        <v>58.21834518985237</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>23.62171601084333</v>
+        <v>23.62171598575661</v>
       </c>
       <c r="J24" s="2" t="n">
         <v>0.6346432281774312</v>
@@ -1736,7 +1736,7 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.1678888716042523</v>
+        <v>-0.1678888710478872</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>60.29423249583816</v>
+        <v>60.29423247763588</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>23.43726713489442</v>
+        <v>23.43726709723093</v>
       </c>
       <c r="J25" s="2" t="n">
         <v>1.637735272203349</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.7470985799138559</v>
+        <v>0.7470985802031578</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1824,10 +1824,10 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>69.90824633488506</v>
+        <v>69.90824630250597</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>36.71325113209628</v>
+        <v>36.71325115355687</v>
       </c>
       <c r="J26" s="2" t="n">
         <v>1.358764037325768</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>1.626590135003279</v>
+        <v>1.626590135203574</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1877,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>60.14462427410668</v>
+        <v>60.14462387642024</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>27.95973680805202</v>
+        <v>27.95973692307105</v>
       </c>
       <c r="J27" s="2" t="n">
         <v>1.98281625398306</v>
@@ -1895,7 +1895,7 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.1706728121128643</v>
+        <v>0.1706728127026031</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>66.10959272038522</v>
+        <v>66.10959277187629</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>38.82875742084621</v>
+        <v>38.82875736052593</v>
       </c>
       <c r="J28" s="2" t="n">
         <v>2.037158419477089</v>
@@ -1948,7 +1948,7 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.7117909652559133</v>
+        <v>0.7117909649221004</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>807.1549612311055</v>
+        <v>807.1549612311056</v>
       </c>
       <c r="E29" s="2" t="n">
         <v>24.65</v>
@@ -1983,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>60.61864264631136</v>
+        <v>60.61864261554427</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>31.14629544912737</v>
+        <v>31.14629538676018</v>
       </c>
       <c r="J29" s="2" t="n">
         <v>0.5533000623860974</v>
@@ -2001,7 +2001,7 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.2382324378325182</v>
+        <v>0.2382324379278675</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>802.332433021734</v>
+        <v>802.3324330217339</v>
       </c>
       <c r="E30" s="2" t="n">
         <v>45.4</v>
@@ -2036,10 +2036,10 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>61.53213114977339</v>
+        <v>61.5321311011632</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20.83621481246016</v>
+        <v>20.83621507258738</v>
       </c>
       <c r="J30" s="2" t="n">
         <v>5.646051563605955</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.330753426113993</v>
+        <v>0.3307534273824868</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2089,10 +2089,10 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>69.56941614386787</v>
+        <v>69.56941616909481</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>25.699294499795</v>
+        <v>25.69929448039495</v>
       </c>
       <c r="J31" s="2" t="n">
         <v>6.856557300808712</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>3.552139129387421</v>
+        <v>3.552139129164882</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>58.17733871894136</v>
+        <v>58.17733871497742</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>13.65803266019826</v>
+        <v>13.6580326157152</v>
       </c>
       <c r="J32" s="2" t="n">
         <v>0.5374173130016149</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>6.800993716108877</v>
+        <v>6.80099371521888</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>57.55460135244225</v>
+        <v>57.55460134160918</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>17.38536039384805</v>
+        <v>17.3853603960706</v>
       </c>
       <c r="J33" s="2" t="n">
         <v>0.6722253325089924</v>
@@ -2213,7 +2213,7 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.2885020185125562</v>
+        <v>0.2885020179562012</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2248,10 +2248,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>60.93048037364278</v>
+        <v>60.9304803573857</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>40.13647676727416</v>
+        <v>40.13647672127134</v>
       </c>
       <c r="J34" s="2" t="n">
         <v>1.110610536017054</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.0158544118180687</v>
+        <v>-0.0158544117958157</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2301,10 +2301,10 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>70.38719538372902</v>
+        <v>70.38719535166183</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>32.37932062668082</v>
+        <v>32.37932066297888</v>
       </c>
       <c r="J35" s="2" t="n">
         <v>0.9221864814963022</v>
@@ -2319,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.5275376161108341</v>
+        <v>0.5275376177799274</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>65.86444599566585</v>
+        <v>65.86444594999665</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>20.3868908494191</v>
+        <v>20.38689086122185</v>
       </c>
       <c r="J36" s="2" t="n">
         <v>0.8755146918912791</v>
@@ -2372,7 +2372,7 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>70.06539485015244</v>
+        <v>70.06539486684267</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>68.29430498802573</v>
+        <v>68.29430497046646</v>
       </c>
       <c r="I37" s="2" t="n">
         <v>32.0953860385156</v>
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.4007844596973164</v>
+        <v>0.400784459764079</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2446,7 +2446,7 @@
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>735.1133125405546</v>
+        <v>735.1133125405555</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>38.05</v>
@@ -2460,10 +2460,10 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>65.39226151095465</v>
+        <v>65.39226114312285</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>37.72796679477382</v>
+        <v>37.72796694132875</v>
       </c>
       <c r="J38" s="2" t="n">
         <v>1.076955423323244</v>
@@ -2478,7 +2478,7 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.3986211967066057</v>
+        <v>0.3986211975300059</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2566,10 +2566,10 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>78.42636828448555</v>
+        <v>78.42636826260494</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>52.96359619150951</v>
+        <v>52.96359619160793</v>
       </c>
       <c r="J40" s="2" t="n">
         <v>1.002387116603794</v>
@@ -2584,7 +2584,7 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>2.660901038888585</v>
+        <v>2.660901038799565</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>56.81809455483162</v>
+        <v>56.81809454940083</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>27.65672652504281</v>
+        <v>27.65672653222695</v>
       </c>
       <c r="J41" s="2" t="n">
         <v>1.122722364768725</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-1.826789401493954</v>
+        <v>-1.826789401716393</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2672,10 +2672,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>61.23027504948998</v>
+        <v>61.23027500983753</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>28.63791921821767</v>
+        <v>28.63791921496253</v>
       </c>
       <c r="J42" s="2" t="n">
         <v>0.5338240457739151</v>
@@ -2690,7 +2690,7 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.3197287707813652</v>
+        <v>0.3197287708370107</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>690.8936040989779</v>
+        <v>690.8936040989778</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>27.95</v>
@@ -2725,10 +2725,10 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>64.55654772389913</v>
+        <v>64.55654769245074</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>28.88532375739664</v>
+        <v>28.88532373402176</v>
       </c>
       <c r="J43" s="2" t="n">
         <v>0.3782811262697764</v>
@@ -2743,7 +2743,7 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.3518805458649227</v>
+        <v>0.35188054578703</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>685.7898084125552</v>
+        <v>685.7898084125553</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>99.40000000000001</v>
@@ -2778,10 +2778,10 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>63.53907149092338</v>
+        <v>63.51610444858202</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>60.75726995059456</v>
+        <v>60.75589887627963</v>
       </c>
       <c r="J44" s="2" t="n">
         <v>0.9653194621989536</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.0528508898366056</v>
+        <v>-0.0528471657539438</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>55.81606937072959</v>
+        <v>55.81606939377352</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>28.44517507478029</v>
+        <v>28.44517507681702</v>
       </c>
       <c r="J45" s="2" t="n">
         <v>0.447132927958286</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.0176086339528437</v>
+        <v>-0.0176086339417221</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>673.8183604662408</v>
+        <v>673.818360466239</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>74.3</v>
@@ -2884,10 +2884,10 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>59.52018689673147</v>
+        <v>59.52018684695069</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>25.83270813267633</v>
+        <v>25.83270808435175</v>
       </c>
       <c r="J46" s="2" t="n">
         <v>0.2741866501919323</v>
@@ -2902,7 +2902,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0952987276200505</v>
+        <v>0.0952987279316159</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>666.6744531969588</v>
+        <v>666.6744531969589</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>17.9</v>
@@ -2937,10 +2937,10 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>58.41316722019191</v>
+        <v>58.41316715217558</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>27.84416519308537</v>
+        <v>27.84416509387505</v>
       </c>
       <c r="J47" s="2" t="n">
         <v>1.199312633526556</v>
@@ -2955,7 +2955,7 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.0337447135479966</v>
+        <v>0.0337447136147588</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
@@ -2976,7 +2976,7 @@
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>664.4914835043749</v>
+        <v>664.491483504375</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>68.90000000000001</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>59.25655297495057</v>
+        <v>59.2565530719535</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>23.43008427082232</v>
+        <v>23.43008440357145</v>
       </c>
       <c r="J48" s="2" t="n">
         <v>1.490835057844686</v>
@@ -3008,7 +3008,7 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>1.097124342226361</v>
+        <v>1.097124341380698</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>54.77681424932954</v>
+        <v>54.77681417734303</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>16.29680399831524</v>
+        <v>16.29680401908981</v>
       </c>
       <c r="J49" s="2" t="n">
         <v>2.184888375613524</v>
@@ -3061,7 +3061,7 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.1108759288422169</v>
+        <v>0.1108759287754513</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
@@ -3096,10 +3096,10 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>57.1571106103292</v>
+        <v>57.15711057220877</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>18.37643424318943</v>
+        <v>18.37643426454401</v>
       </c>
       <c r="J50" s="2" t="n">
         <v>0.6429291810658572</v>
@@ -3114,7 +3114,7 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>1.498138158409806</v>
+        <v>1.498138158676873</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>78.74736856468884</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>23.58618803269447</v>
+        <v>23.58618820382341</v>
       </c>
       <c r="J51" s="2" t="n">
         <v>0.9967911928548756</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.302935212508177</v>
+        <v>0.3029352124525397</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>88.01990014082509</v>
+        <v>88.01989980494112</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>36.33916033774211</v>
+        <v>36.33916131320937</v>
       </c>
       <c r="J52" s="2" t="n">
         <v>0.5729402479523195</v>
@@ -3220,7 +3220,7 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.3456221323424175</v>
+        <v>0.3456221324987907</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3308,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>52.49674931172622</v>
+        <v>52.49674924171195</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>26.2482413080174</v>
+        <v>26.24824136376607</v>
       </c>
       <c r="J54" s="2" t="n">
         <v>0.5040643032148443</v>
@@ -3326,7 +3326,7 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0019101196941255</v>
+        <v>0.0019101197831422</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3361,10 +3361,10 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>54.16815559731925</v>
+        <v>54.16815566619423</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>23.69965988477684</v>
+        <v>23.69965983252558</v>
       </c>
       <c r="J55" s="2" t="n">
         <v>0.632245345795861</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.3506136720797435</v>
+        <v>-0.3506136720352362</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3414,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>66.67182180324697</v>
+        <v>66.67182168262455</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>32.3061092455017</v>
+        <v>32.30610903408729</v>
       </c>
       <c r="J56" s="2" t="n">
         <v>1.151031432412038</v>
@@ -3432,7 +3432,7 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.4031469897677134</v>
+        <v>0.4031469900792768</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>607.5061415532775</v>
+        <v>607.5061415532774</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>14</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>53.15943304156036</v>
+        <v>53.15943312594235</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>8.472045232979839</v>
+        <v>8.472045271489336</v>
       </c>
       <c r="J57" s="2" t="n">
         <v>0.5893034644567916</v>
@@ -3485,7 +3485,7 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.0011813817016056</v>
+        <v>0.001181381679351</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>51.42432268844757</v>
+        <v>51.42432255808885</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>20.36529064877288</v>
+        <v>20.36529064132071</v>
       </c>
       <c r="J58" s="2" t="n">
         <v>0.6799845768712917</v>
@@ -3538,7 +3538,7 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>2.057348262140819</v>
+        <v>2.057348263364813</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3573,10 +3573,10 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>52.32037472815189</v>
+        <v>52.3203747167751</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>9.863708718972989</v>
+        <v>9.863708713934308</v>
       </c>
       <c r="J59" s="2" t="n">
         <v>1.580138880361237</v>
@@ -3591,7 +3591,7 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.2329826479616757</v>
+        <v>0.2329826480284417</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>58.63489639156941</v>
+        <v>58.63490871814086</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>17.16734245442693</v>
+        <v>17.16734536482775</v>
       </c>
       <c r="J60" s="2" t="n">
         <v>0.4074975354292283</v>
@@ -3644,7 +3644,7 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.0147186945330642</v>
+        <v>-0.0147187010535659</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>65.27431008465803</v>
+        <v>65.27431008686852</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>36.61748462085246</v>
+        <v>36.61748453558086</v>
       </c>
       <c r="J61" s="2" t="n">
         <v>0.8011777735130025</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.4788556894004383</v>
+        <v>0.4788556894894551</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3735,7 +3735,7 @@
         <v>52.26935854226889</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>12.93103359380409</v>
+        <v>12.93103350982815</v>
       </c>
       <c r="J62" s="2" t="n">
         <v>2.748753193860966</v>
@@ -3750,7 +3750,7 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.143879486009828</v>
+        <v>-0.1438794861733097</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>570.6576712331699</v>
+        <v>570.6576712331703</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>45.65</v>
@@ -3785,10 +3785,10 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>58.46449926741292</v>
+        <v>58.46449872158443</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>28.8999021483184</v>
+        <v>28.89990214935996</v>
       </c>
       <c r="J63" s="2" t="n">
         <v>0.3050180038402357</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.09132814700285929</v>
+        <v>0.0913281480265604</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3838,10 +3838,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>58.08193065112616</v>
+        <v>58.08193060763711</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>10.56160766964318</v>
+        <v>10.56160768783272</v>
       </c>
       <c r="J64" s="2" t="n">
         <v>1.515627426154144</v>
@@ -3877,7 +3877,7 @@
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>564.500214985046</v>
+        <v>564.5002149850459</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>12.6</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>59.0210247393914</v>
+        <v>59.02102445782641</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>15.229414617035</v>
+        <v>15.22941454190366</v>
       </c>
       <c r="J65" s="2" t="n">
         <v>6.934148303290059</v>
@@ -3909,7 +3909,7 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.0701632664953383</v>
+        <v>0.0701632665175928</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -3944,10 +3944,10 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>53.58832895225821</v>
+        <v>53.58832901283885</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>4.247525626940332</v>
+        <v>4.247525626940331</v>
       </c>
       <c r="J66" s="2" t="n">
         <v>0.2090974515380325</v>
@@ -3962,7 +3962,7 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0013723857875309</v>
+        <v>0.001372385743022</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>52.82989169646092</v>
+        <v>52.82989173213962</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>22.41723156377933</v>
+        <v>22.41723155826916</v>
       </c>
       <c r="J67" s="2" t="n">
         <v>0.7483535274785388</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.0362359041864478</v>
+        <v>0.0362359041641941</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4050,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>51.07922728438911</v>
+        <v>51.07922737673413</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>21.02267042648525</v>
+        <v>21.02267041368824</v>
       </c>
       <c r="J68" s="2" t="n">
         <v>0.4365574536163896</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.2722162729714836</v>
+        <v>0.2722162733052906</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4089,7 +4089,7 @@
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>551.8082713098649</v>
+        <v>551.8082713098651</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>45.7</v>
@@ -4103,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>57.51659430202221</v>
+        <v>57.51659418902656</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>24.11480192249145</v>
+        <v>24.11480197675271</v>
       </c>
       <c r="J69" s="2" t="n">
         <v>0.3334113220005095</v>
@@ -4121,7 +4121,7 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1256526768670149</v>
+        <v>-0.1256526767223595</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>549.8168824265987</v>
+        <v>549.8168824265989</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>31.6</v>
@@ -4156,10 +4156,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>57.73979758092193</v>
+        <v>57.7397975440138</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>30.77486858663044</v>
+        <v>30.77486857306912</v>
       </c>
       <c r="J70" s="2" t="n">
         <v>0.3779651107791265</v>
@@ -4174,7 +4174,7 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.2132874694727659</v>
+        <v>0.2132874694393836</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4209,10 +4209,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>55.42056778558058</v>
+        <v>55.42056779126536</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>10.2995420425184</v>
+        <v>10.29954206092026</v>
       </c>
       <c r="J71" s="2" t="n">
         <v>0.8667252815497062</v>
@@ -4227,7 +4227,7 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0859200090911824</v>
+        <v>0.0859200090466775</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>543.2419206084236</v>
+        <v>543.2419206084235</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>67.59999999999999</v>
@@ -4262,10 +4262,10 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>56.84989070168693</v>
+        <v>56.84989048512296</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>14.55933434214523</v>
+        <v>14.55933440547063</v>
       </c>
       <c r="J72" s="2" t="n">
         <v>0.319663854112855</v>
@@ -4280,7 +4280,7 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.1278474882710328</v>
+        <v>0.1278474890054265</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>542.9692554257805</v>
+        <v>542.9692554257797</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>85</v>
@@ -4315,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>53.29219460372574</v>
+        <v>53.29219450129965</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>13.30245626234925</v>
+        <v>13.30245634045101</v>
       </c>
       <c r="J73" s="2" t="n">
         <v>2.681883259180557</v>
@@ -4333,7 +4333,7 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.5413951036461857</v>
+        <v>0.5413951041357818</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>54.47113773359573</v>
+        <v>54.4711376907477</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>33.70032050486451</v>
+        <v>33.70032062618826</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.4577437211522194</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.350974858793202</v>
+        <v>-0.350974858592912</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>55.1816900016985</v>
+        <v>55.18168970698116</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>39.04840955724337</v>
+        <v>39.04841001792335</v>
       </c>
       <c r="J75" s="2" t="n">
         <v>0.2591149658500514</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.0357385113408506</v>
+        <v>0.0357385116079016</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4474,10 +4474,10 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>66.80883600510377</v>
+        <v>66.80883598595707</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>31.99071139550221</v>
+        <v>31.99071150239562</v>
       </c>
       <c r="J76" s="2" t="n">
         <v>0.6869807903016845</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.5815592727764143</v>
+        <v>0.5815592728431749</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>52.92873951360731</v>
+        <v>52.92873951753912</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>26.4040844436471</v>
+        <v>26.40408442632564</v>
       </c>
       <c r="J77" s="2" t="n">
         <v>2.006382126504294</v>
@@ -4545,7 +4545,7 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>1.065963591263524</v>
+        <v>1.065963591085488</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>526.8458481738521</v>
+        <v>526.8458481738525</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>65.2</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>58.01557024748325</v>
+        <v>58.0155702122911</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>23.33848122353546</v>
+        <v>23.33848093990258</v>
       </c>
       <c r="J78" s="2" t="n">
         <v>0.7940511965114355</v>
@@ -4598,7 +4598,7 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.3154570054644012</v>
+        <v>0.3154570058076574</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>522.4197784960699</v>
+        <v>522.4197784960697</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>246</v>
@@ -4633,10 +4633,10 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>53.74011598074935</v>
+        <v>53.74011597124477</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>28.57092389436645</v>
+        <v>28.57092393624995</v>
       </c>
       <c r="J79" s="2" t="n">
         <v>1.384760666645939</v>
@@ -4651,7 +4651,7 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>2.04217654516002</v>
+        <v>2.042176544937462</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>515.5811968834228</v>
+        <v>515.5811968834225</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>56</v>
@@ -4686,10 +4686,10 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>51.06084516031443</v>
+        <v>51.06084517808077</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>23.99054657031717</v>
+        <v>23.99054665336685</v>
       </c>
       <c r="J80" s="2" t="n">
         <v>0.9131049899276608</v>
@@ -4704,7 +4704,7 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0523373650833563</v>
+        <v>-0.0523373648385571</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>51.66265542540339</v>
+        <v>51.66265541066392</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>18.49436293427526</v>
+        <v>18.49436304701716</v>
       </c>
       <c r="J81" s="2" t="n">
         <v>1.529710217811603</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.4067247239375462</v>
+        <v>0.4067247239820479</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>513.9493079155588</v>
+        <v>513.9493079155586</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>23.85</v>
@@ -4792,10 +4792,10 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>54.90139696904161</v>
+        <v>54.90139681262878</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>13.44033397399243</v>
+        <v>13.4403340725888</v>
       </c>
       <c r="J82" s="2" t="n">
         <v>0.602275264324557</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.207222613611731</v>
+        <v>0.2072226137786372</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4845,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>53.0746889378585</v>
+        <v>53.07468892619333</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>20.04220741716327</v>
+        <v>20.04220744536692</v>
       </c>
       <c r="J83" s="2" t="n">
         <v>0.941116231528476</v>
@@ -4863,7 +4863,7 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.7462597544355734</v>
+        <v>0.7462597539904521</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>511.6332271804632</v>
+        <v>511.6332271804629</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>129.5</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>57.93371603870958</v>
+        <v>57.933715953217</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>17.72495741968742</v>
+        <v>17.72495745483138</v>
       </c>
       <c r="J84" s="2" t="n">
         <v>0.9133972201883788</v>
@@ -4916,7 +4916,7 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.9721422280839968</v>
+        <v>0.9721422285290821</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>510.8217240564245</v>
+        <v>510.8217240564244</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>901</v>
@@ -4951,10 +4951,10 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>50.56233397767091</v>
+        <v>50.56233395791252</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>36.02496797227034</v>
+        <v>36.02496796172826</v>
       </c>
       <c r="J85" s="2" t="n">
         <v>0.440245459880123</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-27.29501793415659</v>
+        <v>-27.29501793348892</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>55.95931510019174</v>
+        <v>55.95931509225989</v>
       </c>
       <c r="I86" s="2" t="n">
         <v>29.28640157033431</v>
@@ -5022,7 +5022,7 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.0609982258464173</v>
+        <v>0.0609982258241638</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>53.02031180690584</v>
+        <v>53.02031180320942</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>24.25507067473984</v>
+        <v>24.25507066714589</v>
       </c>
       <c r="J87" s="2" t="n">
         <v>1.225502955753691</v>
@@ -5075,7 +5075,7 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-4.062838317738976</v>
+        <v>-4.062838317772366</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
@@ -5110,10 +5110,10 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>49.53369419575336</v>
+        <v>49.53369422436816</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>28.93407397514829</v>
+        <v>28.93407396536752</v>
       </c>
       <c r="J88" s="2" t="n">
         <v>0.3586666804839356</v>
@@ -5128,7 +5128,7 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.7229850964540896</v>
+        <v>-0.7229850966432592</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>496.7616655577775</v>
+        <v>496.7616655577774</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>19.95</v>
@@ -5163,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>63.30483404024913</v>
+        <v>63.30483420573216</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>18.46183634445809</v>
+        <v>18.46183635884454</v>
       </c>
       <c r="J89" s="2" t="n">
         <v>0.8650570566434078</v>
@@ -5181,7 +5181,7 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.3527159758436579</v>
+        <v>0.3527159758770415</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>495.5080999184733</v>
+        <v>495.5080999184771</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>33.65</v>
@@ -5216,10 +5216,10 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>70.27427542657554</v>
+        <v>70.27427575529907</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>19.35550493693172</v>
+        <v>19.35550506201307</v>
       </c>
       <c r="J90" s="2" t="n">
         <v>11.53683940844793</v>
@@ -5234,7 +5234,7 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.5341766690282529</v>
+        <v>0.5341766684718962</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>55.55527847537834</v>
+        <v>55.55527848448146</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>16.24636739245034</v>
+        <v>16.24636742006847</v>
       </c>
       <c r="J91" s="2" t="n">
         <v>1.278250770109548</v>
@@ -5287,7 +5287,7 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.4770259080932268</v>
+        <v>0.4770259081154846</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>488.9697062450432</v>
+        <v>488.9697062450422</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>73.3</v>
@@ -5322,10 +5322,10 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>56.84050312077858</v>
+        <v>56.84050306323076</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>15.19200257943902</v>
+        <v>15.19200257943903</v>
       </c>
       <c r="J92" s="2" t="n">
         <v>1.828765695686838</v>
@@ -5340,7 +5340,7 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.3747289588801181</v>
+        <v>0.3747289589691413</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>485.9287671069623</v>
+        <v>485.9287671069619</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>41.45</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>52.56473340268518</v>
+        <v>52.56473341459812</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>20.00600346184982</v>
+        <v>20.0060035504007</v>
       </c>
       <c r="J93" s="2" t="n">
         <v>0.6515106030108712</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.7322167428225104</v>
+        <v>0.7322167427446203</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>483.0658602697317</v>
+        <v>483.0658602697316</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>21.1</v>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>63.08695716592757</v>
+        <v>63.08695714713251</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>32.35591626480861</v>
+        <v>32.35591632190741</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.2336463290885963</v>
@@ -5467,7 +5467,7 @@
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>470.555806867258</v>
+        <v>470.5558068672584</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>31.6</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>55.08098021967093</v>
+        <v>55.08098012090625</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>30.6670619498494</v>
+        <v>30.66706184267316</v>
       </c>
       <c r="J95" s="2" t="n">
         <v>0.5564768477308839</v>
@@ -5499,7 +5499,7 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.2153294278604113</v>
+        <v>0.215329427893795</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>49.12547402685642</v>
+        <v>49.12547399854152</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>23.11894205179462</v>
+        <v>23.11894203794234</v>
       </c>
       <c r="J96" s="2" t="n">
         <v>0.2880366545910341</v>
@@ -5552,7 +5552,7 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.2681981434357668</v>
+        <v>-0.2681981432354737</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>467.8018407383917</v>
+        <v>467.801840738393</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>26.4</v>
@@ -5587,10 +5587,10 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>52.95709330092195</v>
+        <v>52.95709316860053</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>22.2573193300105</v>
+        <v>22.25731944565097</v>
       </c>
       <c r="J97" s="2" t="n">
         <v>1.692165830509133</v>
@@ -5605,7 +5605,7 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.1696771719435463</v>
+        <v>0.1696771720881974</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
@@ -5640,10 +5640,10 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>50.49259809245554</v>
+        <v>50.49259831794107</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>19.19761924429336</v>
+        <v>19.19761913983739</v>
       </c>
       <c r="J98" s="2" t="n">
         <v>0.4732222217671081</v>
@@ -5658,7 +5658,7 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0744582442001606</v>
+        <v>-0.0744582444115837</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>44.83243791491911</v>
+        <v>44.83243785193612</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>25.80143097140458</v>
+        <v>25.80143098227057</v>
       </c>
       <c r="J99" s="2" t="n">
         <v>0.3912502850070979</v>
@@ -5711,7 +5711,7 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-1.68836698444805</v>
+        <v>-1.688366984181004</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
@@ -5746,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>37.88319000013469</v>
+        <v>37.88318990986472</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>30.33776824186238</v>
+        <v>30.33776827342429</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.328519018109024</v>
@@ -5764,7 +5764,7 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.408696176855067</v>
+        <v>0.4086961768995749</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>51.57365252661261</v>
+        <v>51.57365251285891</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>10.57339176201896</v>
+        <v>10.57339176268223</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.293230501522351</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>1.065842414783147</v>
+        <v>1.065842416340973</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>49.07070288827069</v>
+        <v>49.07070287736784</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>10.65147835867334</v>
+        <v>10.65147833844183</v>
       </c>
       <c r="J102" s="2" t="n">
         <v>0.8867405720445148</v>
@@ -5870,7 +5870,7 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.1397540068823819</v>
+        <v>0.1397540069380124</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>439.4422189039535</v>
+        <v>439.4422189039531</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>2410</v>
@@ -5905,10 +5905,10 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>47.79096726663811</v>
+        <v>47.7909672408318</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>9.415020075529441</v>
+        <v>9.415020073930014</v>
       </c>
       <c r="J103" s="2" t="n">
         <v>0.4473475238743477</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>9.304130727035876</v>
+        <v>9.304130721472704</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>49.74706536156252</v>
+        <v>49.74706531520187</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>16.75058124338309</v>
+        <v>16.75058131509029</v>
       </c>
       <c r="J104" s="2" t="n">
         <v>0.4592497276729003</v>
@@ -5976,7 +5976,7 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.7255498580794582</v>
+        <v>-0.7255498576343913</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>436.9083382989696</v>
+        <v>436.9083382989638</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>61.5</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>51.81870189300484</v>
+        <v>51.81870186934135</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>5.731403913743681</v>
+        <v>5.731403871049228</v>
       </c>
       <c r="J105" s="2" t="n">
         <v>1.745862463957025</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.0986231774249835</v>
+        <v>0.0986231779813362</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6064,10 +6064,10 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>34.49763657104963</v>
+        <v>34.4976365481683</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>22.92777303240093</v>
+        <v>22.92777303196644</v>
       </c>
       <c r="J106" s="2" t="n">
         <v>2.82263175611179</v>
@@ -6082,7 +6082,7 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0028949586358906</v>
+        <v>-0.002894958624764</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>50.46431993187829</v>
+        <v>50.46431991483426</v>
       </c>
       <c r="I107" s="2" t="n">
         <v>15.0333089116541</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-4.852318554566985</v>
+        <v>-4.852318555679375</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>57.80189296758745</v>
+        <v>57.80189291187367</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>30.46951963813871</v>
+        <v>30.46951995259474</v>
       </c>
       <c r="J108" s="2" t="n">
         <v>0.1477160668102483</v>
@@ -6188,7 +6188,7 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.6645179782493076</v>
+        <v>0.6645179784718505</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
@@ -6223,10 +6223,10 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>52.3276091462652</v>
+        <v>52.32760914758765</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>13.17222514183875</v>
+        <v>13.17222521944546</v>
       </c>
       <c r="J109" s="2" t="n">
         <v>1.662293121124835</v>
@@ -6276,10 +6276,10 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>49.54969243352448</v>
+        <v>49.54969235731319</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>18.1549865405423</v>
+        <v>18.15498656798</v>
       </c>
       <c r="J110" s="2" t="n">
         <v>0.7875355456852896</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.119228368636492</v>
+        <v>0.1192283686698746</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>49.17057954787504</v>
+        <v>49.17057953014294</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>14.23419357945038</v>
+        <v>14.23419356173238</v>
       </c>
       <c r="J111" s="2" t="n">
         <v>0.5987818026716797</v>
@@ -6347,7 +6347,7 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.2428241390540193</v>
+        <v>0.2428241391875491</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
@@ -6368,7 +6368,7 @@
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>420.7461058963134</v>
+        <v>420.7461058963132</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>206</v>
@@ -6382,10 +6382,10 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>46.46790931751328</v>
+        <v>46.46790924369216</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>10.7360605534524</v>
+        <v>10.73606049133861</v>
       </c>
       <c r="J112" s="2" t="n">
         <v>0.6318077882328406</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.9944337791030576</v>
+        <v>0.9944337802157692</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6435,10 +6435,10 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>48.01849378241813</v>
+        <v>48.01849373143141</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>19.64011580312176</v>
+        <v>19.64011585093357</v>
       </c>
       <c r="J113" s="2" t="n">
         <v>0.521674578412746</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.6242933302972919</v>
+        <v>0.6242933304085609</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>413.7454073532097</v>
+        <v>413.7454073532096</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>21.25</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>51.72803374604634</v>
+        <v>51.72803305597477</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>4.892172893082169</v>
+        <v>4.892172130562852</v>
       </c>
       <c r="J114" s="2" t="n">
         <v>3.410828999694096</v>
@@ -6506,7 +6506,7 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.2464592267023962</v>
+        <v>0.2464592318431339</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>46.60718701623958</v>
+        <v>46.6071869794176</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>20.28071046751299</v>
+        <v>20.28071044104824</v>
       </c>
       <c r="J115" s="2" t="n">
         <v>0.3241424321894683</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.9526694859497032</v>
+        <v>-0.9526694857716632</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6580,7 +6580,7 @@
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>411.0318272085167</v>
+        <v>411.0318272085168</v>
       </c>
       <c r="E116" s="2" t="n">
         <v>25.6</v>
@@ -6594,10 +6594,10 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>51.54370701999677</v>
+        <v>51.54370680308215</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>21.88768695995172</v>
+        <v>21.88768700357075</v>
       </c>
       <c r="J116" s="2" t="n">
         <v>7.244113267170436</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0946540648858451</v>
+        <v>0.0946540650193716</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>52.04974367596014</v>
+        <v>52.049743678728</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>16.41710133305654</v>
+        <v>16.41710132389558</v>
       </c>
       <c r="J117" s="2" t="n">
         <v>0.5001453202099504</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.2538401079299498</v>
+        <v>0.2538401079744553</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6700,10 +6700,10 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>53.1477300641201</v>
+        <v>53.1477300355896</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>11.76152021992988</v>
+        <v>11.76152021550861</v>
       </c>
       <c r="J118" s="2" t="n">
         <v>0.6871457297849558</v>
@@ -6718,7 +6718,7 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.201225452510844</v>
+        <v>0.201225452555355</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>401.8682524513032</v>
+        <v>401.8682524513033</v>
       </c>
       <c r="E119" s="2" t="n">
         <v>53.2</v>
@@ -6753,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>51.58933262459233</v>
+        <v>51.58933261782251</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>9.458058793527998</v>
+        <v>9.458058768625149</v>
       </c>
       <c r="J119" s="2" t="n">
         <v>0.0723271316533375</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-2.193488204196556</v>
+        <v>-2.193488204018531</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>401.1735124413417</v>
+        <v>401.17351244134</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>7.11</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>47.12959346931158</v>
+        <v>47.12959333782159</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>24.73313633592875</v>
+        <v>24.73313637548496</v>
       </c>
       <c r="J120" s="2" t="n">
         <v>0.4825239345707466</v>
@@ -6824,7 +6824,7 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0125307676295716</v>
+        <v>0.0125307676073174</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
@@ -6859,10 +6859,10 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>54.32015030681346</v>
+        <v>54.32015027756131</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>26.59866577388376</v>
+        <v>26.59866580685824</v>
       </c>
       <c r="J121" s="2" t="n">
         <v>0.4066821163780484</v>
@@ -6877,7 +6877,7 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.2192538609026562</v>
+        <v>0.2192538609137826</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
@@ -6912,10 +6912,10 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>48.7025348256393</v>
+        <v>48.70253485309998</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>9.21548947408991</v>
+        <v>9.215489499500602</v>
       </c>
       <c r="J122" s="2" t="n">
         <v>2.092393199534332</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.1684565827880091</v>
+        <v>0.1684565827546239</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>51.42734320775916</v>
+        <v>51.42734310248067</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>18.20392821210588</v>
+        <v>18.20392824066227</v>
       </c>
       <c r="J123" s="2" t="n">
         <v>0.5918397564193401</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.8599497137103298</v>
+        <v>-0.8599497127088984</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -7004,7 +7004,7 @@
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>392.0480030757702</v>
+        <v>392.0480030757701</v>
       </c>
       <c r="E124" s="2" t="n">
         <v>166</v>
@@ -7018,10 +7018,10 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>42.09359722588825</v>
+        <v>42.09359721874781</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>21.72071838400424</v>
+        <v>21.72071831704341</v>
       </c>
       <c r="J124" s="2" t="n">
         <v>0.6212137910245693</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-2.933432070679564</v>
+        <v>-2.93343207066841</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7071,10 +7071,10 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>48.26534228702744</v>
+        <v>48.26534192651625</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>22.91413233714543</v>
+        <v>22.91413239288371</v>
       </c>
       <c r="J125" s="2" t="n">
         <v>0.7275578511605162</v>
@@ -7089,7 +7089,7 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>1.099672273793525</v>
+        <v>1.099672274349901</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>39.84062286778468</v>
+        <v>39.8406228318449</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>42.94665027801086</v>
+        <v>42.94665041124024</v>
       </c>
       <c r="J126" s="2" t="n">
         <v>1.135770415781296</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.5368822282950534</v>
+        <v>0.53688222896269</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7177,10 +7177,10 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>45.83737476986276</v>
+        <v>45.83737460716816</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>14.29764608553387</v>
+        <v>14.29764601704993</v>
       </c>
       <c r="J127" s="2" t="n">
         <v>0.6426344857095315</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.0529394249379564</v>
+        <v>0.0529394249824677</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7230,10 +7230,10 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>44.42983475725421</v>
+        <v>44.42983471135963</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>22.77973687334746</v>
+        <v>22.77973694903622</v>
       </c>
       <c r="J128" s="2" t="n">
         <v>0.3072575363480952</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-2.034152035527255</v>
+        <v>-2.034152035193422</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7283,10 +7283,10 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>44.22690421088168</v>
+        <v>44.22690428842809</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>31.06597313854142</v>
+        <v>31.06597315517536</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.2173958519070449</v>
@@ -7336,10 +7336,10 @@
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>52.5848618135031</v>
+        <v>52.58486183662914</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>16.46047752320021</v>
+        <v>16.46047751937406</v>
       </c>
       <c r="J130" s="2" t="n">
         <v>0.5885021000919567</v>
@@ -7354,7 +7354,7 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>0.1909838553185652</v>
+        <v>0.190983855312025</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>373.1227370608755</v>
+        <v>373.122737060875</v>
       </c>
       <c r="E131" s="2" t="n">
         <v>61.5</v>
@@ -7389,10 +7389,10 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>49.34603358625171</v>
+        <v>49.34603360915872</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>11.00222460103178</v>
+        <v>11.00222452688966</v>
       </c>
       <c r="J131" s="2" t="n">
         <v>0.7467470749551198</v>
@@ -7407,7 +7407,7 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.312326502052446</v>
+        <v>0.3123265018521578</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>371.7519365093635</v>
+        <v>371.7519365093638</v>
       </c>
       <c r="E132" s="2" t="n">
         <v>378</v>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>37.45779825049929</v>
+        <v>37.45779823161743</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>10.50542266037648</v>
+        <v>10.50542268461864</v>
       </c>
       <c r="J132" s="2" t="n">
         <v>0.7794784172074235</v>
@@ -7460,7 +7460,7 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-2.955374852418973</v>
+        <v>-2.955374852151925</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
@@ -7495,10 +7495,10 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>47.20392553887792</v>
+        <v>47.20392545334549</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>5.733475259222229</v>
+        <v>5.733475232623106</v>
       </c>
       <c r="J133" s="2" t="n">
         <v>0.439031728674581</v>
@@ -7513,7 +7513,7 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>-0.3311641983100619</v>
+        <v>-0.3311641964184395</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
@@ -7548,10 +7548,10 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>43.38927871274372</v>
+        <v>43.38927869743127</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>8.805314763010724</v>
+        <v>8.805314665518278</v>
       </c>
       <c r="J134" s="2" t="n">
         <v>0.4128509071776405</v>
@@ -7566,7 +7566,7 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>-0.0200883600720915</v>
+        <v>-0.0200883600832152</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>41.85586850162802</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>20.63258207415718</v>
+        <v>20.63258200457364</v>
       </c>
       <c r="J135" s="2" t="n">
         <v>0.4901777989916768</v>
@@ -7654,10 +7654,10 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>52.99794124941917</v>
+        <v>52.99794122175098</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>13.02893511178756</v>
+        <v>13.02893513151622</v>
       </c>
       <c r="J136" s="2" t="n">
         <v>0.7086853104413622</v>
@@ -7672,7 +7672,7 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.1733534584660824</v>
+        <v>0.1733534585328416</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
@@ -7707,10 +7707,10 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>59.1309943842196</v>
+        <v>59.13099427987934</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>23.18640310114059</v>
+        <v>23.18640312349707</v>
       </c>
       <c r="J137" s="2" t="n">
         <v>0.3623921022045773</v>
@@ -7725,7 +7725,7 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.1302223386157149</v>
+        <v>0.1302223386713502</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>362.0917715694626</v>
+        <v>362.0917715694544</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>20.35</v>
@@ -7760,10 +7760,10 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>44.24995870288041</v>
+        <v>44.24995831003666</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>25.14902447881119</v>
+        <v>25.14902443445792</v>
       </c>
       <c r="J138" s="2" t="n">
         <v>0.2634774768903227</v>
@@ -7778,7 +7778,7 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>0.0926193734148585</v>
+        <v>0.09261937354838309</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
@@ -7813,10 +7813,10 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>51.57895025422862</v>
+        <v>51.57895026056282</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>5.91170785219271</v>
+        <v>5.911707849079677</v>
       </c>
       <c r="J139" s="2" t="n">
         <v>1.812958229949816</v>
@@ -7831,7 +7831,7 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>0.2017707196070501</v>
+        <v>0.2017707195514143</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>359.7762367402207</v>
+        <v>359.7762367402208</v>
       </c>
       <c r="E140" s="2" t="n">
         <v>103</v>
@@ -7866,10 +7866,10 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>44.51538618445012</v>
+        <v>44.51538611042812</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>20.81967089163802</v>
+        <v>20.8196709464247</v>
       </c>
       <c r="J140" s="2" t="n">
         <v>0.2964235255700025</v>
@@ -7884,7 +7884,7 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>0.2406183786595983</v>
+        <v>0.2406183791269227</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>43.31390851093528</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>16.65434466641809</v>
+        <v>16.65434475536065</v>
       </c>
       <c r="J141" s="2" t="n">
         <v>1.016227227482118</v>
@@ -7972,10 +7972,10 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>51.21504095682264</v>
+        <v>51.21504098012016</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>30.22092405952742</v>
+        <v>30.22092400471644</v>
       </c>
       <c r="J142" s="2" t="n">
         <v>0.5537829690031607</v>
@@ -7990,7 +7990,7 @@
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-0.0817575576431491</v>
+        <v>-0.081757557576385</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>350.6544780349947</v>
+        <v>350.6544780349945</v>
       </c>
       <c r="E143" s="2" t="n">
         <v>161</v>
@@ -8025,10 +8025,10 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>39.55753403506539</v>
+        <v>39.5575339156908</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>18.11988934130044</v>
+        <v>18.11988937253901</v>
       </c>
       <c r="J143" s="2" t="n">
         <v>0.3342551803549092</v>
@@ -8043,7 +8043,7 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>0.1039943022211993</v>
+        <v>0.1039943034451873</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>346.0091951773201</v>
+        <v>346.009195177321</v>
       </c>
       <c r="E144" s="2" t="n">
         <v>698</v>
@@ -8078,7 +8078,7 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>47.04005705793491</v>
+        <v>47.04005705272849</v>
       </c>
       <c r="I144" s="2" t="n">
         <v>8.348994905778941</v>
@@ -8096,7 +8096,7 @@
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>-0.4109228341051416</v>
+        <v>-0.4109228351067067</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
@@ -8131,10 +8131,10 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>53.49407457560054</v>
+        <v>53.49407450657281</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>18.05380525772092</v>
+        <v>18.05380550912933</v>
       </c>
       <c r="J145" s="2" t="n">
         <v>0.5674653250095503</v>
@@ -8149,7 +8149,7 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>0.1498907198927589</v>
+        <v>0.149890720782938</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
@@ -8184,10 +8184,10 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>35.69395879159011</v>
+        <v>35.69395897278551</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>21.4260726483414</v>
+        <v>21.42607263575928</v>
       </c>
       <c r="J146" s="2" t="n">
         <v>0.3206128635313185</v>
@@ -8202,7 +8202,7 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>0.0639674525373411</v>
+        <v>0.0639674523815615</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
@@ -8237,10 +8237,10 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>40.78431727753252</v>
+        <v>40.78431725725395</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>20.48792830866852</v>
+        <v>20.48792832063343</v>
       </c>
       <c r="J147" s="2" t="n">
         <v>0.4071510081378914</v>
@@ -8255,7 +8255,7 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>0.0296612236551783</v>
+        <v>0.0296612236663054</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
@@ -8290,10 +8290,10 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>50.56251120847067</v>
+        <v>50.5625109929811</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>25.93134300054706</v>
+        <v>25.93134307752268</v>
       </c>
       <c r="J148" s="2" t="n">
         <v>0.2351420323570064</v>
@@ -8308,7 +8308,7 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-0.0765711875526771</v>
+        <v>-0.0765711873746423</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
@@ -8329,7 +8329,7 @@
         <v/>
       </c>
       <c r="D149" s="2" t="n">
-        <v>332.052207548237</v>
+        <v>332.0522075482375</v>
       </c>
       <c r="E149" s="2" t="n">
         <v>14.8</v>
@@ -8346,7 +8346,7 @@
         <v>52.87142602450996</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>17.56150917481012</v>
+        <v>17.56150917452257</v>
       </c>
       <c r="J149" s="2" t="n">
         <v>0.665769176672532</v>
@@ -8361,7 +8361,7 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>0.1307241110372862</v>
+        <v>0.1307241110039051</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
@@ -8396,10 +8396,10 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>45.63285064604919</v>
+        <v>45.63285063386068</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>18.61398452542189</v>
+        <v>18.61398460571754</v>
       </c>
       <c r="J150" s="2" t="n">
         <v>0.3306712997812749</v>
@@ -8414,7 +8414,7 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>-0.5718090199903157</v>
+        <v>-0.5718090199680577</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v/>
       </c>
       <c r="D151" s="2" t="n">
-        <v>324.4098094768397</v>
+        <v>324.4098094768398</v>
       </c>
       <c r="E151" s="2" t="n">
         <v>513</v>
@@ -8449,10 +8449,10 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>46.18345623996108</v>
+        <v>46.1834562345737</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>11.02633389767196</v>
+        <v>11.02633393219116</v>
       </c>
       <c r="J151" s="2" t="n">
         <v>0.5932838706177282</v>
@@ -8467,7 +8467,7 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>-5.074116120189955</v>
+        <v>-5.074116120635046</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
@@ -8502,10 +8502,10 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>48.10831046145258</v>
+        <v>48.10831037163665</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>9.166451779538887</v>
+        <v>9.16645164210995</v>
       </c>
       <c r="J152" s="2" t="n">
         <v>1.109280930033654</v>
@@ -8520,7 +8520,7 @@
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>0.1917169577685309</v>
+        <v>0.1917169579576921</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>38.61430823278304</v>
+        <v>38.6143081615845</v>
       </c>
       <c r="I153" s="2" t="n">
         <v>42.11423741862148</v>
@@ -8573,7 +8573,7 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>0.3355509876244289</v>
+        <v>0.335550987605361</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
@@ -8608,10 +8608,10 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>41.57158963104342</v>
+        <v>41.57158960266897</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>19.43724573560995</v>
+        <v>19.43724578264203</v>
       </c>
       <c r="J154" s="2" t="n">
         <v>0.1056765127628301</v>
@@ -8626,7 +8626,7 @@
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>-0.06752920079692649</v>
+        <v>-0.0675292007412906</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v/>
       </c>
       <c r="D155" s="2" t="n">
-        <v>315.331153934144</v>
+        <v>315.3311539341441</v>
       </c>
       <c r="E155" s="2" t="n">
         <v>40.2</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>39.68222255463586</v>
+        <v>39.68222232007376</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>21.15331626372</v>
+        <v>21.1533164380309</v>
       </c>
       <c r="J155" s="2" t="n">
         <v>1.245482279421965</v>
@@ -8679,7 +8679,7 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>-0.2181264236544496</v>
+        <v>-0.2181264232538682</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>48.35855716242697</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>9.817544242958094</v>
+        <v>9.817544346772756</v>
       </c>
       <c r="J156" s="2" t="n">
         <v>0.4997571661287222</v>
@@ -8732,7 +8732,7 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>0.0287185737876893</v>
+        <v>0.0287185738433245</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
@@ -8767,10 +8767,10 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>41.34193706352144</v>
+        <v>41.34193726818538</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>36.44494499555905</v>
+        <v>36.44494500672952</v>
       </c>
       <c r="J157" s="2" t="n">
         <v>0.4314336617328781</v>
@@ -8785,7 +8785,7 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>0.6614459655788432</v>
+        <v>0.6614459668028498</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
@@ -8820,10 +8820,10 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>40.89801646856558</v>
+        <v>40.89801631187449</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>25.38867607461387</v>
+        <v>25.38867618836161</v>
       </c>
       <c r="J158" s="2" t="n">
         <v>0.6090715119090011</v>
@@ -8838,7 +8838,7 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>0.4226591117205718</v>
+        <v>0.422659112388204</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
         <v/>
       </c>
       <c r="D159" s="2" t="n">
-        <v>306.1316572010385</v>
+        <v>306.1316572010387</v>
       </c>
       <c r="E159" s="2" t="n">
         <v>99.7</v>
@@ -8873,10 +8873,10 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>51.80466945879562</v>
+        <v>51.80466930079765</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>18.80077031919863</v>
+        <v>18.80077040536696</v>
       </c>
       <c r="J159" s="2" t="n">
         <v>0.5203972432773276</v>
@@ -8891,7 +8891,7 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>0.2386846254874157</v>
+        <v>0.2386846264888593</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v/>
       </c>
       <c r="D160" s="2" t="n">
-        <v>304.5740754238821</v>
+        <v>304.5740754238814</v>
       </c>
       <c r="E160" s="2" t="n">
         <v>78.5</v>
@@ -8926,10 +8926,10 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>31.39648460989247</v>
+        <v>31.3964841425265</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>27.97941887552145</v>
+        <v>27.97941893482285</v>
       </c>
       <c r="J160" s="2" t="n">
         <v>0.4061833674589742</v>
@@ -8944,7 +8944,7 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>-0.512280060532011</v>
+        <v>-0.5122800590187153</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
@@ -8979,10 +8979,10 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>46.2572385659147</v>
+        <v>46.25723853814677</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>23.95788301752827</v>
+        <v>23.95788299921623</v>
       </c>
       <c r="J161" s="2" t="n">
         <v>0.633836254137858</v>
@@ -8997,7 +8997,7 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>0.0862199022434928</v>
+        <v>0.0862199022657484</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
@@ -9032,10 +9032,10 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>51.8971291383917</v>
+        <v>51.89712915250618</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>18.58156692636146</v>
+        <v>18.58156686718599</v>
       </c>
       <c r="J162" s="2" t="n">
         <v>1.006434342233889</v>
@@ -9050,7 +9050,7 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>23.23606975435544</v>
+        <v>23.23606975101704</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
@@ -9085,10 +9085,10 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>43.26727849696328</v>
+        <v>43.26727843662459</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>23.64453494380736</v>
+        <v>23.64453491751511</v>
       </c>
       <c r="J163" s="2" t="n">
         <v>0.3406349543769466</v>
@@ -9103,7 +9103,7 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>0.1834733354709172</v>
+        <v>0.1834733356378242</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
@@ -9124,7 +9124,7 @@
         <v/>
       </c>
       <c r="D164" s="2" t="n">
-        <v>288.4625288623504</v>
+        <v>288.4625288623495</v>
       </c>
       <c r="E164" s="2" t="n">
         <v>182.5</v>
@@ -9138,10 +9138,10 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>54.26808025627501</v>
+        <v>54.26808017129474</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>11.97989740366489</v>
+        <v>11.97989739981883</v>
       </c>
       <c r="J164" s="2" t="n">
         <v>0.7904062940324069</v>
@@ -9156,7 +9156,7 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>1.169116030314798</v>
+        <v>1.169116031538785</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
@@ -9191,10 +9191,10 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>46.50814117145381</v>
+        <v>46.50814107407415</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>13.2755512568241</v>
+        <v>13.27555132510089</v>
       </c>
       <c r="J165" s="2" t="n">
         <v>0.4781743917911729</v>
@@ -9209,7 +9209,7 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>0.1472209433963136</v>
+        <v>0.1472209435966024</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v/>
       </c>
       <c r="D166" s="2" t="n">
-        <v>287.3397847110577</v>
+        <v>287.3397847110573</v>
       </c>
       <c r="E166" s="2" t="n">
         <v>42.15</v>
@@ -9244,10 +9244,10 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>51.38318664646331</v>
+        <v>51.38318664134987</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>12.37532031275081</v>
+        <v>12.37532029904241</v>
       </c>
       <c r="J166" s="2" t="n">
         <v>0.2254141711834608</v>
@@ -9262,7 +9262,7 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>0.5378699537860735</v>
+        <v>0.5378699538083274</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
@@ -9297,7 +9297,7 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>43.02782780292721</v>
+        <v>43.02782775151884</v>
       </c>
       <c r="I167" s="2" t="n">
         <v>17.87816970476102</v>
@@ -9315,7 +9315,7 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>0.1696961814611637</v>
+        <v>0.1696961815056719</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v/>
       </c>
       <c r="D168" s="2" t="n">
-        <v>285.5131991137751</v>
+        <v>285.513199113775</v>
       </c>
       <c r="E168" s="2" t="n">
         <v>50.3</v>
@@ -9350,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>45.57161898018442</v>
+        <v>45.57161886907972</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>18.37430624191653</v>
+        <v>18.37430625539125</v>
       </c>
       <c r="J168" s="2" t="n">
         <v>0.454714111392245</v>
@@ -9368,7 +9368,7 @@
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>0.3515741288856315</v>
+        <v>0.3515741291526844</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
@@ -9403,10 +9403,10 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>38.78436838619973</v>
+        <v>38.7843683080424</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>11.52867015023618</v>
+        <v>11.5286701572507</v>
       </c>
       <c r="J169" s="2" t="n">
         <v>0.7373651866710851</v>
@@ -9421,7 +9421,7 @@
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>-1.170619091525329</v>
+        <v>-1.170619091336168</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>49.19138894100186</v>
+        <v>49.19138836163021</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>13.55275131135225</v>
+        <v>13.55275140399204</v>
       </c>
       <c r="J170" s="2" t="n">
         <v>0.5420062022786005</v>
@@ -9474,7 +9474,7 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>0.0666244622904473</v>
+        <v>0.0666244625908799</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v/>
       </c>
       <c r="D171" s="2" t="n">
-        <v>279.1952278226266</v>
+        <v>279.1952278226281</v>
       </c>
       <c r="E171" s="2" t="n">
         <v>41.25</v>
@@ -9509,10 +9509,10 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>50.96296186173326</v>
+        <v>50.96296180869454</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>16.74922172477383</v>
+        <v>16.74922174587012</v>
       </c>
       <c r="J171" s="2" t="n">
         <v>0.3333917647610592</v>
@@ -9527,7 +9527,7 @@
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>0.102656366400652</v>
+        <v>0.1026563664785424</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
@@ -9562,10 +9562,10 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>46.23541351223167</v>
+        <v>46.23541352184191</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>14.27112281273554</v>
+        <v>14.27112278237403</v>
       </c>
       <c r="J172" s="2" t="n">
         <v>0.384194537522191</v>
@@ -9580,7 +9580,7 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>0.2161877449307915</v>
+        <v>0.2161877448528988</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>42.03105099446837</v>
+        <v>42.03105106907329</v>
       </c>
       <c r="I173" s="2" t="n">
         <v>11.23120578988346</v>
@@ -9633,7 +9633,7 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>-0.0220059604740787</v>
+        <v>-0.0220059604963364</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
@@ -9668,10 +9668,10 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>46.88013320185718</v>
+        <v>46.88013319548953</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>16.42968032334678</v>
+        <v>16.42968032807357</v>
       </c>
       <c r="J174" s="2" t="n">
         <v>0.5575251084374677</v>
@@ -9686,7 +9686,7 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-0.2668556483850831</v>
+        <v>-0.266855648318318</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
@@ -9721,10 +9721,10 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>39.61134419480405</v>
+        <v>39.61134415971062</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>31.78151449908198</v>
+        <v>31.78151447960147</v>
       </c>
       <c r="J175" s="2" t="n">
         <v>0.2911042501545425</v>
@@ -9739,7 +9739,7 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>0.3654463287349392</v>
+        <v>0.3654463287683227</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
@@ -9774,10 +9774,10 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>47.04086510003325</v>
+        <v>47.04086470105052</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>8.371803217059307</v>
+        <v>8.371803223166632</v>
       </c>
       <c r="J176" s="2" t="n">
         <v>0.3864822905953792</v>
@@ -9792,7 +9792,7 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>0.2610426487560247</v>
+        <v>0.2610426493123832</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
@@ -9827,10 +9827,10 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>51.62764091334794</v>
+        <v>51.62764086058568</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>35.38701422269337</v>
+        <v>35.38701422849721</v>
       </c>
       <c r="J177" s="2" t="n">
         <v>0.4192700410840189</v>
@@ -9845,7 +9845,7 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>0.02544579615727</v>
+        <v>0.0254457961795253</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
@@ -9880,10 +9880,10 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>45.70941917809253</v>
+        <v>45.70941886393128</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>14.49515801629096</v>
+        <v>14.49515808899554</v>
       </c>
       <c r="J178" s="2" t="n">
         <v>0.2552239948841377</v>
@@ -9898,7 +9898,7 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>-0.6171027855892541</v>
+        <v>-0.6171027819172838</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v/>
       </c>
       <c r="D179" s="2" t="n">
-        <v>261.5049683288456</v>
+        <v>261.5049683288455</v>
       </c>
       <c r="E179" s="2" t="n">
         <v>60.3</v>
@@ -9933,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>28.13757289255188</v>
+        <v>28.13757263850012</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>19.41471890936596</v>
+        <v>19.41471896782178</v>
       </c>
       <c r="J179" s="2" t="n">
         <v>1.070798334939756</v>
@@ -9951,7 +9951,7 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>0.0560125500619221</v>
+        <v>0.0560125502844663</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
@@ -9986,10 +9986,10 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>39.05516881974161</v>
+        <v>39.05516874684572</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>14.9281916681353</v>
+        <v>14.92819164896107</v>
       </c>
       <c r="J180" s="2" t="n">
         <v>0.0437134502923976</v>
@@ -10004,7 +10004,7 @@
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>-2.305344970139839</v>
+        <v>-2.305344969527848</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v/>
       </c>
       <c r="D181" s="2" t="n">
-        <v>259.7949388876981</v>
+        <v>259.7949388876982</v>
       </c>
       <c r="E181" s="2" t="n">
         <v>122</v>
@@ -10039,10 +10039,10 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>47.608383124118</v>
+        <v>47.60838299661973</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>10.01925375999575</v>
+        <v>10.01925381108427</v>
       </c>
       <c r="J181" s="2" t="n">
         <v>0.7850988528511064</v>
@@ -10057,7 +10057,7 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>0.4903637979802566</v>
+        <v>0.4903637982027882</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v/>
       </c>
       <c r="D182" s="2" t="n">
-        <v>255.7815133847074</v>
+        <v>255.7815133847075</v>
       </c>
       <c r="E182" s="2" t="n">
         <v>104</v>
@@ -10092,10 +10092,10 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>48.63296647852606</v>
+        <v>48.63296650666343</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>10.21380099512586</v>
+        <v>10.21380095653909</v>
       </c>
       <c r="J182" s="2" t="n">
         <v>0.6785101273992737</v>
@@ -10110,7 +10110,7 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>0.8890340431754229</v>
+        <v>0.8890340432199402</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
@@ -10131,7 +10131,7 @@
         <v/>
       </c>
       <c r="D183" s="2" t="n">
-        <v>254.3819145565139</v>
+        <v>254.381914556514</v>
       </c>
       <c r="E183" s="2" t="n">
         <v>653</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>41.77346198694138</v>
+        <v>41.77346197214754</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>16.17258419120375</v>
+        <v>16.17258419718802</v>
       </c>
       <c r="J183" s="2" t="n">
         <v>0.4335019514652792</v>
@@ -10163,7 +10163,7 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>-4.71377967088241</v>
+        <v>-4.713779670548558</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
@@ -10198,10 +10198,10 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>47.39636172511529</v>
+        <v>47.39636176530768</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>18.24161561824787</v>
+        <v>18.24161563605631</v>
       </c>
       <c r="J184" s="2" t="n">
         <v>0.3192697865532485</v>
@@ -10216,7 +10216,7 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>0.0310787336536124</v>
+        <v>0.031078733675867</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
@@ -10237,7 +10237,7 @@
         <v/>
       </c>
       <c r="D185" s="2" t="n">
-        <v>249.9094847718254</v>
+        <v>249.9094847718252</v>
       </c>
       <c r="E185" s="2" t="n">
         <v>27.3</v>
@@ -10251,10 +10251,10 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>44.6483421447281</v>
+        <v>44.64834270672752</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>17.91381507185823</v>
+        <v>17.91381529849921</v>
       </c>
       <c r="J185" s="2" t="n">
         <v>0.7684671936753076</v>
@@ -10269,7 +10269,7 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>0.062913441772282</v>
+        <v>0.0629134418612987</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v/>
       </c>
       <c r="D186" s="2" t="n">
-        <v>243.9432647290009</v>
+        <v>243.9432647290011</v>
       </c>
       <c r="E186" s="2" t="n">
         <v>19.9</v>
@@ -10304,10 +10304,10 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>34.58677267594727</v>
+        <v>34.58677218616553</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>35.6965907854936</v>
+        <v>35.69659081375372</v>
       </c>
       <c r="J186" s="2" t="n">
         <v>0.1934081488626786</v>
@@ -10322,7 +10322,7 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>-0.1212948784237782</v>
+        <v>-0.1212948780343242</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
@@ -10357,10 +10357,10 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>43.59365322687039</v>
+        <v>43.5936532728542</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>17.10958421274027</v>
+        <v>17.10958430295524</v>
       </c>
       <c r="J187" s="2" t="n">
         <v>0.4976044403896267</v>
@@ -10375,7 +10375,7 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>0.021860229048042</v>
+        <v>0.02186022905917</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v/>
       </c>
       <c r="D188" s="2" t="n">
-        <v>235.0483683838806</v>
+        <v>235.0483683838809</v>
       </c>
       <c r="E188" s="2" t="n">
         <v>652</v>
@@ -10410,10 +10410,10 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>47.27195609423827</v>
+        <v>47.27195609673169</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>19.26413927474908</v>
+        <v>19.26413915657768</v>
       </c>
       <c r="J188" s="2" t="n">
         <v>0.3624515946954439</v>
@@ -10428,7 +10428,7 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>-10.19451845726875</v>
+        <v>-10.19451845804768</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
@@ -10463,10 +10463,10 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>34.8428833703129</v>
+        <v>34.84288323742209</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>23.04368344334643</v>
+        <v>23.04368356973874</v>
       </c>
       <c r="J189" s="2" t="n">
         <v>0.5282416522659487</v>
@@ -10481,7 +10481,7 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>-0.0631773903292238</v>
+        <v>-0.0631773902958382</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
@@ -10516,10 +10516,10 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>46.77426936214098</v>
+        <v>46.77426930536542</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>13.73828789791971</v>
+        <v>13.73828804212404</v>
       </c>
       <c r="J190" s="2" t="n">
         <v>0.2591908265976749</v>
@@ -10534,7 +10534,7 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>-0.0075714736945244</v>
+        <v>-0.0075714736388816</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>50.93390951603405</v>
+        <v>50.93390953247821</v>
       </c>
       <c r="I191" s="2" t="n">
         <v>25.54229446200077</v>
@@ -10587,7 +10587,7 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>0.3277367147032692</v>
+        <v>0.3277367146921411</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
@@ -10608,7 +10608,7 @@
         <v/>
       </c>
       <c r="D192" s="2" t="n">
-        <v>220.8366424488549</v>
+        <v>220.8366424488552</v>
       </c>
       <c r="E192" s="2" t="n">
         <v>14</v>
@@ -10625,7 +10625,7 @@
         <v>38.65705426897056</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>14.91962117223156</v>
+        <v>14.91962117223155</v>
       </c>
       <c r="J192" s="2" t="n">
         <v>0.08958135705464371</v>
@@ -10640,7 +10640,7 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>-0.0224784325918771</v>
+        <v>-0.0224784325807503</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v/>
       </c>
       <c r="D193" s="2" t="n">
-        <v>219.8242724282755</v>
+        <v>219.824272428275</v>
       </c>
       <c r="E193" s="2" t="n">
         <v>10.5</v>
@@ -10675,10 +10675,10 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>44.16630739271048</v>
+        <v>44.16630741425373</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>33.65499039261265</v>
+        <v>33.65499041159423</v>
       </c>
       <c r="J193" s="2" t="n">
         <v>0.2794921370641668</v>
@@ -10693,7 +10693,7 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>-0.0300961401090633</v>
+        <v>-0.0300961401313183</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
@@ -10714,7 +10714,7 @@
         <v/>
       </c>
       <c r="D194" s="2" t="n">
-        <v>215.5818471401686</v>
+        <v>215.5818471401692</v>
       </c>
       <c r="E194" s="2" t="n">
         <v>58.3</v>
@@ -10728,10 +10728,10 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>52.31353247425698</v>
+        <v>52.3135323584107</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>17.71037293625317</v>
+        <v>17.71037294787111</v>
       </c>
       <c r="J194" s="2" t="n">
         <v>0.5675688184263168</v>
@@ -10746,7 +10746,7 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>0.1825992712062227</v>
+        <v>0.1825992713842583</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v/>
       </c>
       <c r="D195" s="2" t="n">
-        <v>214.9219248483569</v>
+        <v>214.9219248483568</v>
       </c>
       <c r="E195" s="2" t="n">
         <v>35.2</v>
@@ -10781,10 +10781,10 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>43.40730773649717</v>
+        <v>43.40730774744784</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>14.61515335188473</v>
+        <v>14.61515337824558</v>
       </c>
       <c r="J195" s="2" t="n">
         <v>0.467855320986675</v>
@@ -10799,7 +10799,7 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>-0.1901915743862998</v>
+        <v>-0.1901915743306603</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
@@ -10820,7 +10820,7 @@
         <v/>
       </c>
       <c r="D196" s="2" t="n">
-        <v>210.0841015446434</v>
+        <v>210.0841015446433</v>
       </c>
       <c r="E196" s="2" t="n">
         <v>51</v>
@@ -10834,10 +10834,10 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>52.56529868475364</v>
+        <v>52.56529854278871</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>14.06841846391618</v>
+        <v>14.06841852711609</v>
       </c>
       <c r="J196" s="2" t="n">
         <v>0.5421491004646335</v>
@@ -10852,7 +10852,7 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>0.1965699218303901</v>
+        <v>0.1965699221419497</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
@@ -10887,10 +10887,10 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>46.58338787905806</v>
+        <v>46.5833878587993</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>11.28692572734666</v>
+        <v>11.28692574200344</v>
       </c>
       <c r="J197" s="2" t="n">
         <v>0.3976344190683007</v>
@@ -10905,7 +10905,7 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>0.9539714881934492</v>
+        <v>0.95397148812668</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
@@ -10940,10 +10940,10 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>38.52468738492916</v>
+        <v>38.52468736834384</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>37.05643639838571</v>
+        <v>37.0564364149939</v>
       </c>
       <c r="J198" s="2" t="n">
         <v>0.2184035076860174</v>
@@ -10958,7 +10958,7 @@
         <v>-1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>0.6704926587072642</v>
+        <v>0.6704926585959745</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v/>
       </c>
       <c r="D199" s="2" t="n">
-        <v>199.2889140286702</v>
+        <v>199.2889140286703</v>
       </c>
       <c r="E199" s="2" t="n">
         <v>174</v>
@@ -10993,10 +10993,10 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>38.22585984792831</v>
+        <v>38.22586000076379</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>23.83100221008213</v>
+        <v>23.83100223643229</v>
       </c>
       <c r="J199" s="2" t="n">
         <v>0.2853829753307409</v>
@@ -11011,7 +11011,7 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>-2.11234911724192</v>
+        <v>-2.112349117019366</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v/>
       </c>
       <c r="D200" s="2" t="n">
-        <v>198.1574127017284</v>
+        <v>198.1574127017282</v>
       </c>
       <c r="E200" s="2" t="n">
         <v>37.9</v>
@@ -11046,10 +11046,10 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>31.95778432370442</v>
+        <v>31.957784075611</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>15.63401047274968</v>
+        <v>15.63401063196648</v>
       </c>
       <c r="J200" s="2" t="n">
         <v>1.196010165141951</v>
@@ -11064,7 +11064,7 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>-0.0902748370948242</v>
+        <v>-0.0902748369835558</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
@@ -11085,7 +11085,7 @@
         <v/>
       </c>
       <c r="D201" s="2" t="n">
-        <v>195.7109791899732</v>
+        <v>195.7109791899734</v>
       </c>
       <c r="E201" s="2" t="n">
         <v>77.09999999999999</v>
@@ -11099,10 +11099,10 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>44.11258736805052</v>
+        <v>44.11258731192758</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>14.53794902951426</v>
+        <v>14.5379491243999</v>
       </c>
       <c r="J201" s="2" t="n">
         <v>0.4063902882826609</v>
@@ -11117,7 +11117,7 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>-0.5511757300907072</v>
+        <v>-0.5511757297568965</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
@@ -11152,10 +11152,10 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>29.84643053458743</v>
+        <v>29.8464305173778</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>58.0745059067189</v>
+        <v>58.07450603166586</v>
       </c>
       <c r="J202" s="2" t="n">
         <v>0.4905875454765599</v>
@@ -11170,7 +11170,7 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>0.5493708902966441</v>
+        <v>0.5493708901853784</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
@@ -11205,10 +11205,10 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>33.17251754521899</v>
+        <v>33.1725174892124</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>28.56067908889364</v>
+        <v>28.56067920665241</v>
       </c>
       <c r="J203" s="2" t="n">
         <v>0.4792301118158766</v>
@@ -11223,7 +11223,7 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>0.0621842437768132</v>
+        <v>0.0621842438880926</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
@@ -11258,10 +11258,10 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>45.37750872380226</v>
+        <v>45.37750882426</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>11.7575266860422</v>
+        <v>11.75752665673949</v>
       </c>
       <c r="J204" s="2" t="n">
         <v>0.8808588173468305</v>
@@ -11276,7 +11276,7 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>-0.07907613749895789</v>
+        <v>-0.0790761373876432</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
@@ -11311,10 +11311,10 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>29.01722089929555</v>
+        <v>29.01722101649714</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>30.21850639642134</v>
+        <v>30.21850641973694</v>
       </c>
       <c r="J205" s="2" t="n">
         <v>0.5652406291312982</v>
@@ -11329,7 +11329,7 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>-0.2617420104152437</v>
+        <v>-0.2617420104375003</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         <v/>
       </c>
       <c r="D206" s="2" t="n">
-        <v>182.3726822288274</v>
+        <v>182.3726822288289</v>
       </c>
       <c r="E206" s="2" t="n">
         <v>110.5</v>
@@ -11364,10 +11364,10 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>50.72930171640248</v>
+        <v>50.72930172621219</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>13.77881192339523</v>
+        <v>13.77881193497391</v>
       </c>
       <c r="J206" s="2" t="n">
         <v>0.3830540577101557</v>
@@ -11382,7 +11382,7 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>-0.09809526702862841</v>
+        <v>-0.09809526665031131</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v/>
       </c>
       <c r="D207" s="2" t="n">
-        <v>162.9305267838002</v>
+        <v>162.9305267838003</v>
       </c>
       <c r="E207" s="2" t="n">
         <v>48.2</v>
@@ -11417,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>34.64399070597013</v>
+        <v>34.64399074184308</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>17.09337361624689</v>
+        <v>17.0933736406207</v>
       </c>
       <c r="J207" s="2" t="n">
         <v>0.3982888792338676</v>
@@ -11435,7 +11435,7 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-0.0332885153613569</v>
+        <v>-0.0332885153502324</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
@@ -11470,10 +11470,10 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>39.39771049208377</v>
+        <v>39.39771031856007</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>16.33067010170964</v>
+        <v>16.33067019554443</v>
       </c>
       <c r="J208" s="2" t="n">
         <v>0.7955577684178937</v>
@@ -11488,7 +11488,7 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>0.08360429946088779</v>
+        <v>0.0836042996277979</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
@@ -11523,10 +11523,10 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>41.16931276059569</v>
+        <v>41.16931255883026</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>22.96575194606943</v>
+        <v>22.96575198791308</v>
       </c>
       <c r="J209" s="2" t="n">
         <v>0.1180651104121889</v>
@@ -11541,7 +11541,7 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>0.3424916631626451</v>
+        <v>0.3424916634742048</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
@@ -11576,10 +11576,10 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>47.89640022451787</v>
+        <v>47.89640028606001</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>17.86092190742775</v>
+        <v>17.86092193134143</v>
       </c>
       <c r="J210" s="2" t="n">
         <v>0.4043678615126545</v>
@@ -11594,7 +11594,7 @@
         <v>-1</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>0.1370978238714602</v>
+        <v>0.137097823771317</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
@@ -11629,10 +11629,10 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>44.37292994748754</v>
+        <v>44.37292990266174</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>19.1038180430056</v>
+        <v>19.10381799829786</v>
       </c>
       <c r="J211" s="2" t="n">
         <v>0.6497971648231401</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>0.7238090895852611</v>
+        <v>0.7238090901416152</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11682,10 +11682,10 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>46.67326755309348</v>
+        <v>46.67326751709075</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>17.53420184259065</v>
+        <v>17.53420185838381</v>
       </c>
       <c r="J212" s="2" t="n">
         <v>0.2835473786635566</v>
@@ -11721,7 +11721,7 @@
         <v/>
       </c>
       <c r="D213" s="2" t="n">
-        <v>137.4314706466339</v>
+        <v>137.4314706466281</v>
       </c>
       <c r="E213" s="2" t="n">
         <v>68.3</v>
@@ -11735,10 +11735,10 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>49.73196170669712</v>
+        <v>49.73196191838237</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>14.11397463581732</v>
+        <v>14.11397472369821</v>
       </c>
       <c r="J213" s="2" t="n">
         <v>0.5047933977906637</v>
@@ -11753,7 +11753,7 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>-0.0150251607458176</v>
+        <v>-0.0150251605677797</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v/>
       </c>
       <c r="D214" s="2" t="n">
-        <v>137.2380145251097</v>
+        <v>137.2380145251095</v>
       </c>
       <c r="E214" s="2" t="n">
         <v>22.85</v>
@@ -11788,7 +11788,7 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>35.20521621067009</v>
+        <v>35.2052160541092</v>
       </c>
       <c r="I214" s="2" t="n">
         <v>12.04151699505592</v>
@@ -11806,7 +11806,7 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>-0.0141270205211844</v>
+        <v>-0.0141270204432926</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
@@ -11816,21 +11816,21 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>3523</v>
+        <v>3540</v>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>迎輝</t>
+          <t>曜越</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
         <v/>
       </c>
       <c r="D215" s="2" t="n">
-        <v>129.4026749030052</v>
+        <v>125.9436585116174</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>14.95</v>
+        <v>22.75</v>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
@@ -11841,16 +11841,16 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>48.84424561302122</v>
+        <v>49.04378272773824</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>15.94753029499698</v>
+        <v>19.74189419964191</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>0.7545957296597667</v>
+        <v>0.1384763513731558</v>
       </c>
       <c r="K215" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L215" s="2" t="n">
         <v>0</v>
@@ -11859,31 +11859,31 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>0.0383927486988476</v>
+        <v>-0.0527104472054855</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>3540</v>
+        <v>3492</v>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>曜越</t>
+          <t>長盛</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
         <v/>
       </c>
       <c r="D216" s="2" t="n">
-        <v>125.9436585116174</v>
+        <v>125.5142859710014</v>
       </c>
       <c r="E216" s="2" t="n">
-        <v>22.75</v>
+        <v>19.15</v>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
@@ -11894,16 +11894,16 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>49.04378282547003</v>
+        <v>40.61371734076518</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>19.74189416567811</v>
+        <v>11.21686480668861</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>0.1384763513731558</v>
+        <v>0.2582770506607649</v>
       </c>
       <c r="K216" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L216" s="2" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>-0.052710447327883</v>
+        <v>0.1110412918814525</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
@@ -11922,21 +11922,21 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>3492</v>
+        <v>3484</v>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>長盛</t>
+          <t>崧騰</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
         <v/>
       </c>
       <c r="D217" s="2" t="n">
-        <v>125.5142859710014</v>
+        <v>106.0387330942158</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>19.15</v>
+        <v>46.25</v>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
@@ -11947,16 +11947,16 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>40.61371756671651</v>
+        <v>46.29663030796053</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>11.21686480633752</v>
+        <v>16.47089062894075</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>0.2582770506607649</v>
+        <v>0.3801791620712966</v>
       </c>
       <c r="K217" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L217" s="2" t="n">
         <v>0</v>
@@ -11965,7 +11965,7 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>0.1110412917479304</v>
+        <v>0.184072163742831</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
@@ -11975,21 +11975,21 @@
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>3484</v>
+        <v>3150</v>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>崧騰</t>
+          <t>鈺寶-創</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
         <v/>
       </c>
       <c r="D218" s="2" t="n">
-        <v>106.0387330942158</v>
+        <v>104.8231432872837</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>46.25</v>
+        <v>15.35</v>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
@@ -12000,16 +12000,16 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>46.29663027208385</v>
+        <v>37.54012148535384</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>16.47089058207355</v>
+        <v>12.07796399191621</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>0.3801791620712966</v>
+        <v>0.3130017307264982</v>
       </c>
       <c r="K218" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L218" s="2" t="n">
         <v>0</v>
@@ -12018,7 +12018,7 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>0.1840721636871898</v>
+        <v>-0.0103652569525453</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
@@ -12028,21 +12028,21 @@
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>3150</v>
+        <v>3521</v>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>鈺寶-創</t>
+          <t>鴻翊</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
         <v/>
       </c>
       <c r="D219" s="2" t="n">
-        <v>104.8231432872837</v>
+        <v>94.96559799731592</v>
       </c>
       <c r="E219" s="2" t="n">
-        <v>15.35</v>
+        <v>11.8</v>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
@@ -12053,13 +12053,13 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>37.54012114014884</v>
+        <v>40.0114324047301</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>12.07796392364952</v>
+        <v>14.80551807558729</v>
       </c>
       <c r="J219" s="2" t="n">
-        <v>0.3130017307264982</v>
+        <v>0.2498481353990211</v>
       </c>
       <c r="K219" s="2" t="n">
         <v>0</v>
@@ -12071,7 +12071,7 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>-0.0103652568078903</v>
+        <v>-0.0240196439158716</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
@@ -12081,21 +12081,21 @@
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>3521</v>
+        <v>3527</v>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>鴻翊</t>
+          <t>聚積</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
         <v/>
       </c>
       <c r="D220" s="2" t="n">
-        <v>94.96559799732042</v>
+        <v>90.79118794509108</v>
       </c>
       <c r="E220" s="2" t="n">
-        <v>11.8</v>
+        <v>51</v>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
@@ -12106,16 +12106,16 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>40.01143225300314</v>
+        <v>50.25773210927612</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>14.80551809012956</v>
+        <v>14.16688042080866</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>0.2498481353990211</v>
+        <v>0.3655885215003501</v>
       </c>
       <c r="K220" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L220" s="2" t="n">
         <v>0</v>
@@ -12124,7 +12124,7 @@
         <v>-1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>-0.0240196438491088</v>
+        <v>0.3190265751993297</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
@@ -12134,21 +12134,21 @@
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>3527</v>
+        <v>3373</v>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>聚積</t>
+          <t>熱映</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
         <v/>
       </c>
       <c r="D221" s="2" t="n">
-        <v>90.79118794509112</v>
+        <v>78.71211735523029</v>
       </c>
       <c r="E221" s="2" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
@@ -12159,16 +12159,16 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>50.25773205207906</v>
+        <v>43.04862163921353</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>14.16688044040262</v>
+        <v>10.36997587329762</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>0.3655885215003501</v>
+        <v>0.5073702856040477</v>
       </c>
       <c r="K221" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L221" s="2" t="n">
         <v>0</v>
@@ -12177,7 +12177,7 @@
         <v>-1</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>0.3190265752215814</v>
+        <v>0.0136539161474613</v>
       </c>
       <c r="O221" s="2" t="inlineStr">
         <is>
@@ -12187,21 +12187,21 @@
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
-        <v>3373</v>
+        <v>3259</v>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>熱映</t>
+          <t>鑫創</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
         <v/>
       </c>
       <c r="D222" s="2" t="n">
-        <v>78.71211735523029</v>
+        <v>76.88135887361368</v>
       </c>
       <c r="E222" s="2" t="n">
-        <v>16</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
@@ -12212,13 +12212,13 @@
         <v>0</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>43.04862166754791</v>
+        <v>44.1190946009931</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>10.36997594025252</v>
+        <v>12.51873318490949</v>
       </c>
       <c r="J222" s="2" t="n">
-        <v>0.5073702856040477</v>
+        <v>0.9613365516793488</v>
       </c>
       <c r="K222" s="2" t="n">
         <v>0</v>
@@ -12230,7 +12230,7 @@
         <v>-1</v>
       </c>
       <c r="N222" s="2" t="n">
-        <v>0.0136539161585887</v>
+        <v>0.0393229268990611</v>
       </c>
       <c r="O222" s="2" t="inlineStr">
         <is>
@@ -12240,21 +12240,21 @@
     </row>
     <row r="223">
       <c r="A223" s="2" t="n">
-        <v>3259</v>
+        <v>3257</v>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>鑫創</t>
+          <t>虹冠電</t>
         </is>
       </c>
       <c r="C223" s="2" t="n">
         <v/>
       </c>
       <c r="D223" s="2" t="n">
-        <v>76.88135887361368</v>
+        <v>74.85521857823943</v>
       </c>
       <c r="E223" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>48.7</v>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
@@ -12265,13 +12265,13 @@
         <v>0</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>44.11909462483294</v>
+        <v>46.96525059633765</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>12.51873316392325</v>
+        <v>15.58301312380761</v>
       </c>
       <c r="J223" s="2" t="n">
-        <v>0.9613365516793488</v>
+        <v>0.3781150598065702</v>
       </c>
       <c r="K223" s="2" t="n">
         <v>0</v>
@@ -12283,7 +12283,7 @@
         <v>-1</v>
       </c>
       <c r="N223" s="2" t="n">
-        <v>0.039322926821171</v>
+        <v>0.3319642137356373</v>
       </c>
       <c r="O223" s="2" t="inlineStr">
         <is>
@@ -12293,21 +12293,21 @@
     </row>
     <row r="224">
       <c r="A224" s="2" t="n">
-        <v>3257</v>
+        <v>3523</v>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>虹冠電</t>
+          <t>迎輝</t>
         </is>
       </c>
       <c r="C224" s="2" t="n">
         <v/>
       </c>
       <c r="D224" s="2" t="n">
-        <v>74.85521857823912</v>
+        <v>69.40267490300523</v>
       </c>
       <c r="E224" s="2" t="n">
-        <v>48.7</v>
+        <v>14.95</v>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
@@ -12318,13 +12318,13 @@
         <v>0</v>
       </c>
       <c r="H224" s="2" t="n">
-        <v>46.96525075073376</v>
+        <v>48.84424304977897</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>15.58301305034657</v>
+        <v>15.94753066633572</v>
       </c>
       <c r="J224" s="2" t="n">
-        <v>0.3781150598065702</v>
+        <v>0.7545957296597667</v>
       </c>
       <c r="K224" s="2" t="n">
         <v>0</v>
@@ -12336,7 +12336,7 @@
         <v>-1</v>
       </c>
       <c r="N224" s="2" t="n">
-        <v>0.3319642134908434</v>
+        <v>0.0383927525599627</v>
       </c>
       <c r="O224" s="2" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v/>
       </c>
       <c r="D225" s="2" t="n">
-        <v>63.02822050295413</v>
+        <v>63.0282205029541</v>
       </c>
       <c r="E225" s="2" t="n">
         <v>9.5</v>
@@ -12371,10 +12371,10 @@
         <v>0</v>
       </c>
       <c r="H225" s="2" t="n">
-        <v>45.70343865428038</v>
+        <v>45.70343862181969</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>19.20010531014862</v>
+        <v>19.20010550890374</v>
       </c>
       <c r="J225" s="2" t="n">
         <v>1.055784627332064</v>
@@ -12389,7 +12389,7 @@
         <v>-1</v>
       </c>
       <c r="N225" s="2" t="n">
-        <v>0.0591181191671453</v>
+        <v>0.0591181193502159</v>
       </c>
       <c r="O225" s="2" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         <v/>
       </c>
       <c r="D226" s="2" t="n">
-        <v>56.85602446759344</v>
+        <v>56.85602446758734</v>
       </c>
       <c r="E226" s="2" t="n">
         <v>27.85</v>
@@ -12424,10 +12424,10 @@
         <v>0</v>
       </c>
       <c r="H226" s="2" t="n">
-        <v>43.86931034852221</v>
+        <v>43.86931050762205</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>18.13334872818614</v>
+        <v>18.13334873638076</v>
       </c>
       <c r="J226" s="2" t="n">
         <v>0.4345678402509355</v>
@@ -12442,7 +12442,7 @@
         <v>-1</v>
       </c>
       <c r="N226" s="2" t="n">
-        <v>0.1599528785845019</v>
+        <v>0.1599528786178834</v>
       </c>
       <c r="O226" s="2" t="inlineStr">
         <is>
